--- a/input/reg_unemployment.xlsx
+++ b/input/reg_unemployment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFiles\99 DEV ENV\JAS-MINE\SimPaths\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFiles\99 DEV ENV\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62771247-2D8A-437A-9F7A-39B0F4D7B65E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{788E7650-F9FB-423B-B256-A540CD4A015F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CC9AB010-6F1C-42A2-A1E7-CC06071EB15C}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="3" activeTab="12" xr2:uid="{CC9AB010-6F1C-42A2-A1E7-CC06071EB15C}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -371,7 +371,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
@@ -381,7 +381,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="11" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -733,12 +732,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5DD3FED-033E-405B-A2A7-67A35968B641}">
   <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -746,7 +745,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>70</v>
       </c>
@@ -754,7 +753,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -762,7 +761,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -770,11 +769,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
@@ -782,7 +781,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -793,7 +792,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -801,7 +800,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -809,7 +808,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -817,7 +816,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -826,7 +825,7 @@
         <v>Probit regression estimates of unemployment for male graduates (aged 18 to 64)</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>67</v>
       </c>
@@ -835,7 +834,7 @@
         <v>Probit regression estimates of unemployment for male non-graduates (aged 18 to 64)</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -844,7 +843,7 @@
         <v>Probit regression estimates of unemployment for female graduates (aged 18 to 64)</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>69</v>
       </c>
@@ -860,14 +859,14 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28EC0B5F-04C9-4F5F-A901-B8AAE6DEDE0A}">
-  <dimension ref="A1:BH66"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AX66"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="8.85546875" style="4"/>
-    <col min="5" max="16384" width="8.85546875" style="5"/>
+    <col min="1" max="4" width="8.81640625" style="4"/>
+    <col min="5" max="16384" width="8.81640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
@@ -1018,18 +1017,8 @@
       <c r="AX1" s="4">
         <v>2024</v>
       </c>
-      <c r="AY1" s="4"/>
-      <c r="AZ1" s="4"/>
-      <c r="BA1" s="4"/>
-      <c r="BB1" s="4"/>
-      <c r="BC1" s="4"/>
-      <c r="BD1" s="4"/>
-      <c r="BE1" s="4"/>
-      <c r="BF1" s="4"/>
-      <c r="BG1" s="4"/>
-      <c r="BH1" s="4"/>
     </row>
-    <row r="2" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="6">
         <v>16</v>
       </c>
@@ -1181,7 +1170,7 @@
         <v>0.32057885000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>17</v>
       </c>
@@ -1333,7 +1322,7 @@
         <v>0.24913356000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
         <v>18</v>
       </c>
@@ -1485,7 +1474,7 @@
         <v>0.19593476999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
         <v>19</v>
       </c>
@@ -1637,7 +1626,7 @@
         <v>0.17182712999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <v>20</v>
       </c>
@@ -1789,7 +1778,7 @@
         <v>0.15967402</v>
       </c>
     </row>
-    <row r="7" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>21</v>
       </c>
@@ -1941,7 +1930,7 @@
         <v>0.13140270999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <v>22</v>
       </c>
@@ -2093,7 +2082,7 @@
         <v>0.1082795</v>
       </c>
     </row>
-    <row r="9" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>23</v>
       </c>
@@ -2245,7 +2234,7 @@
         <v>8.8274959999999986E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>24</v>
       </c>
@@ -2397,7 +2386,7 @@
         <v>6.5812979999999993E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
         <v>25</v>
       </c>
@@ -2549,7 +2538,7 @@
         <v>5.5256269999999996E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" s="6">
         <v>26</v>
       </c>
@@ -2701,7 +2690,7 @@
         <v>3.6772130000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
         <v>27</v>
       </c>
@@ -2853,7 +2842,7 @@
         <v>3.6527290000000004E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="6">
         <v>28</v>
       </c>
@@ -3005,7 +2994,7 @@
         <v>2.6608559999999996E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="6">
         <v>29</v>
       </c>
@@ -3157,7 +3146,7 @@
         <v>2.5161919999999997E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="6">
         <v>30</v>
       </c>
@@ -3309,7 +3298,7 @@
         <v>2.468074E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="6">
         <v>31</v>
       </c>
@@ -3461,7 +3450,7 @@
         <v>1.5728199999999998E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="6">
         <v>32</v>
       </c>
@@ -3613,7 +3602,7 @@
         <v>2.0821219999999998E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="6">
         <v>33</v>
       </c>
@@ -3765,7 +3754,7 @@
         <v>1.7944900000000003E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="6">
         <v>34</v>
       </c>
@@ -3917,7 +3906,7 @@
         <v>1.3482890000000001E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="6">
         <v>35</v>
       </c>
@@ -4069,7 +4058,7 @@
         <v>1.324671E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="6">
         <v>36</v>
       </c>
@@ -4221,7 +4210,7 @@
         <v>1.6916359999999998E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" s="6">
         <v>37</v>
       </c>
@@ -4373,7 +4362,7 @@
         <v>1.8430700000000001E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="6">
         <v>38</v>
       </c>
@@ -4525,7 +4514,7 @@
         <v>1.3897240000000002E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="6">
         <v>39</v>
       </c>
@@ -4677,7 +4666,7 @@
         <v>1.690589E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="6">
         <v>40</v>
       </c>
@@ -4829,7 +4818,7 @@
         <v>1.564217E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="6">
         <v>41</v>
       </c>
@@ -4981,7 +4970,7 @@
         <v>1.845892E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="6">
         <v>42</v>
       </c>
@@ -5133,7 +5122,7 @@
         <v>2.5302109999999999E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="6">
         <v>43</v>
       </c>
@@ -5285,7 +5274,7 @@
         <v>2.0708589999999999E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="6">
         <v>44</v>
       </c>
@@ -5437,7 +5426,7 @@
         <v>2.0847170000000005E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="6">
         <v>45</v>
       </c>
@@ -5589,7 +5578,7 @@
         <v>1.7571759999999999E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A32" s="6">
         <v>46</v>
       </c>
@@ -5741,7 +5730,7 @@
         <v>1.7073720000000001E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="6">
         <v>47</v>
       </c>
@@ -5893,7 +5882,7 @@
         <v>2.44919E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="6">
         <v>48</v>
       </c>
@@ -6045,7 +6034,7 @@
         <v>2.5936340000000002E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="6">
         <v>49</v>
       </c>
@@ -6197,7 +6186,7 @@
         <v>2.3026539999999998E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="6">
         <v>50</v>
       </c>
@@ -6349,7 +6338,7 @@
         <v>2.5105870000000002E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="6">
         <v>51</v>
       </c>
@@ -6501,7 +6490,7 @@
         <v>1.7104889999999998E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="6">
         <v>52</v>
       </c>
@@ -6653,7 +6642,7 @@
         <v>2.5441709999999999E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="6">
         <v>53</v>
       </c>
@@ -6805,7 +6794,7 @@
         <v>2.0940939999999998E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="6">
         <v>54</v>
       </c>
@@ -6957,7 +6946,7 @@
         <v>3.389872E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="6">
         <v>55</v>
       </c>
@@ -7109,7 +7098,7 @@
         <v>3.100603E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="6">
         <v>56</v>
       </c>
@@ -7261,7 +7250,7 @@
         <v>2.6832839999999997E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="6">
         <v>57</v>
       </c>
@@ -7413,7 +7402,7 @@
         <v>3.1260670000000004E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A44" s="6">
         <v>58</v>
       </c>
@@ -7565,7 +7554,7 @@
         <v>2.4161920000000003E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="6">
         <v>59</v>
       </c>
@@ -7717,7 +7706,7 @@
         <v>2.5432729999999997E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="6">
         <v>60</v>
       </c>
@@ -7869,7 +7858,7 @@
         <v>3.0238820000000007E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="6">
         <v>61</v>
       </c>
@@ -8021,7 +8010,7 @@
         <v>2.2392189999999999E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A48" s="6">
         <v>62</v>
       </c>
@@ -8173,7 +8162,7 @@
         <v>2.741072E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="6">
         <v>63</v>
       </c>
@@ -8325,7 +8314,7 @@
         <v>2.356635E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="6">
         <v>64</v>
       </c>
@@ -8477,7 +8466,7 @@
         <v>3.1952790000000002E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="6">
         <v>65</v>
       </c>
@@ -8629,7 +8618,7 @@
         <v>3.9330740624999992E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="6">
         <v>66</v>
       </c>
@@ -8781,7 +8770,7 @@
         <v>4.6708691249999996E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="6">
         <v>67</v>
       </c>
@@ -8933,7 +8922,7 @@
         <v>5.4086641875000008E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="6">
         <v>68</v>
       </c>
@@ -9085,7 +9074,7 @@
         <v>6.1464592499999991E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A55" s="6">
         <v>69</v>
       </c>
@@ -9237,7 +9226,7 @@
         <v>6.8842543125000003E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A56" s="6">
         <v>70</v>
       </c>
@@ -9389,7 +9378,7 @@
         <v>7.6220493750000007E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A57" s="6">
         <v>71</v>
       </c>
@@ -9541,7 +9530,7 @@
         <v>8.3598444375000011E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A58" s="6">
         <v>72</v>
       </c>
@@ -9693,7 +9682,7 @@
         <v>9.0976395000000015E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A59" s="6">
         <v>73</v>
       </c>
@@ -9845,7 +9834,7 @@
         <v>9.8354345625000006E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A60" s="6">
         <v>74</v>
       </c>
@@ -9997,7 +9986,7 @@
         <v>0.10573229625000002</v>
       </c>
     </row>
-    <row r="61" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A61" s="6">
         <v>75</v>
       </c>
@@ -10149,7 +10138,7 @@
         <v>0.11311024687500001</v>
       </c>
     </row>
-    <row r="62" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A62" s="6">
         <v>76</v>
       </c>
@@ -10301,7 +10290,7 @@
         <v>0.12048819750000002</v>
       </c>
     </row>
-    <row r="63" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A63" s="6">
         <v>77</v>
       </c>
@@ -10453,7 +10442,7 @@
         <v>0.12786614812500002</v>
       </c>
     </row>
-    <row r="64" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A64" s="6">
         <v>78</v>
       </c>
@@ -10605,7 +10594,7 @@
         <v>0.13524409875000004</v>
       </c>
     </row>
-    <row r="65" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A65" s="6">
         <v>79</v>
       </c>
@@ -10757,7 +10746,7 @@
         <v>0.14262204937500006</v>
       </c>
     </row>
-    <row r="66" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A66" s="6">
         <v>80</v>
       </c>
@@ -10916,14 +10905,14 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9172C708-9303-4B74-B36A-400E8C4455B4}">
-  <dimension ref="A1:BH66"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AX66"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="8.85546875" style="4"/>
-    <col min="3" max="16384" width="8.85546875" style="5"/>
+    <col min="1" max="2" width="8.81640625" style="4"/>
+    <col min="3" max="16384" width="8.81640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
@@ -11074,18 +11063,8 @@
       <c r="AX1" s="4">
         <v>2024</v>
       </c>
-      <c r="AY1" s="4"/>
-      <c r="AZ1" s="4"/>
-      <c r="BA1" s="4"/>
-      <c r="BB1" s="4"/>
-      <c r="BC1" s="4"/>
-      <c r="BD1" s="4"/>
-      <c r="BE1" s="4"/>
-      <c r="BF1" s="4"/>
-      <c r="BG1" s="4"/>
-      <c r="BH1" s="4"/>
     </row>
-    <row r="2" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="6">
         <v>16</v>
       </c>
@@ -11237,7 +11216,7 @@
         <v>0.32057885000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>17</v>
       </c>
@@ -11389,7 +11368,7 @@
         <v>0.24913356000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
         <v>18</v>
       </c>
@@ -11541,7 +11520,7 @@
         <v>0.19593476999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
         <v>19</v>
       </c>
@@ -11693,7 +11672,7 @@
         <v>0.17182712999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <v>20</v>
       </c>
@@ -11845,7 +11824,7 @@
         <v>0.15967402</v>
       </c>
     </row>
-    <row r="7" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>21</v>
       </c>
@@ -11997,7 +11976,7 @@
         <v>0.13140270999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <v>22</v>
       </c>
@@ -12149,7 +12128,7 @@
         <v>0.1082795</v>
       </c>
     </row>
-    <row r="9" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>23</v>
       </c>
@@ -12301,7 +12280,7 @@
         <v>9.5490260000000007E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>24</v>
       </c>
@@ -12453,7 +12432,7 @@
         <v>8.6285799999999996E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
         <v>25</v>
       </c>
@@ -12605,7 +12584,7 @@
         <v>7.5845690000000007E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" s="6">
         <v>26</v>
       </c>
@@ -12757,7 +12736,7 @@
         <v>5.0565230000000003E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
         <v>27</v>
       </c>
@@ -12909,7 +12888,7 @@
         <v>5.3880789999999998E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="6">
         <v>28</v>
       </c>
@@ -13061,7 +13040,7 @@
         <v>4.4968840000000003E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="6">
         <v>29</v>
       </c>
@@ -13213,7 +13192,7 @@
         <v>3.7355399999999997E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:60" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="6">
         <v>30</v>
       </c>
@@ -13365,7 +13344,7 @@
         <v>3.4893949999999993E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="6">
         <v>31</v>
       </c>
@@ -13517,7 +13496,7 @@
         <v>3.1849840000000004E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="6">
         <v>32</v>
       </c>
@@ -13669,7 +13648,7 @@
         <v>3.3739389999999994E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="6">
         <v>33</v>
       </c>
@@ -13821,7 +13800,7 @@
         <v>2.798235E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="6">
         <v>34</v>
       </c>
@@ -13973,7 +13952,7 @@
         <v>2.8765629999999997E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="6">
         <v>35</v>
       </c>
@@ -14125,7 +14104,7 @@
         <v>2.9261849999999999E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="6">
         <v>36</v>
       </c>
@@ -14277,7 +14256,7 @@
         <v>2.8418540000000003E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" s="6">
         <v>37</v>
       </c>
@@ -14429,7 +14408,7 @@
         <v>2.8308900000000005E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="6">
         <v>38</v>
       </c>
@@ -14581,7 +14560,7 @@
         <v>2.5911989999999996E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="6">
         <v>39</v>
       </c>
@@ -14733,7 +14712,7 @@
         <v>3.2470720000000002E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="6">
         <v>40</v>
       </c>
@@ -14885,7 +14864,7 @@
         <v>2.8177269999999997E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="6">
         <v>41</v>
       </c>
@@ -15037,7 +15016,7 @@
         <v>2.7782039999999997E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="6">
         <v>42</v>
       </c>
@@ -15189,7 +15168,7 @@
         <v>2.7246860000000001E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="6">
         <v>43</v>
       </c>
@@ -15341,7 +15320,7 @@
         <v>2.7496179999999999E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="6">
         <v>44</v>
       </c>
@@ -15493,7 +15472,7 @@
         <v>2.6858360000000005E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="6">
         <v>45</v>
       </c>
@@ -15645,7 +15624,7 @@
         <v>3.0459229999999997E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A32" s="6">
         <v>46</v>
       </c>
@@ -15797,7 +15776,7 @@
         <v>2.7958719999999999E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="6">
         <v>47</v>
       </c>
@@ -15949,7 +15928,7 @@
         <v>3.191956E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="6">
         <v>48</v>
       </c>
@@ -16101,7 +16080,7 @@
         <v>2.8831089999999997E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="6">
         <v>49</v>
       </c>
@@ -16253,7 +16232,7 @@
         <v>3.1578700000000001E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="6">
         <v>50</v>
       </c>
@@ -16405,7 +16384,7 @@
         <v>2.8726309999999998E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="6">
         <v>51</v>
       </c>
@@ -16557,7 +16536,7 @@
         <v>2.8136230000000002E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="6">
         <v>52</v>
       </c>
@@ -16709,7 +16688,7 @@
         <v>3.225426E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="6">
         <v>53</v>
       </c>
@@ -16861,7 +16840,7 @@
         <v>2.4534540000000001E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="6">
         <v>54</v>
       </c>
@@ -17013,7 +16992,7 @@
         <v>3.5306339999999999E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="6">
         <v>55</v>
       </c>
@@ -17165,7 +17144,7 @@
         <v>3.5951499999999997E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="6">
         <v>56</v>
       </c>
@@ -17317,7 +17296,7 @@
         <v>3.3881160000000007E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="6">
         <v>57</v>
       </c>
@@ -17469,7 +17448,7 @@
         <v>3.6523029999999998E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A44" s="6">
         <v>58</v>
       </c>
@@ -17621,7 +17600,7 @@
         <v>3.5319530000000002E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="6">
         <v>59</v>
       </c>
@@ -17773,7 +17752,7 @@
         <v>3.3760220000000001E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="6">
         <v>60</v>
       </c>
@@ -17925,7 +17904,7 @@
         <v>3.87558E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="6">
         <v>61</v>
       </c>
@@ -18077,7 +18056,7 @@
         <v>4.1845160000000006E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A48" s="6">
         <v>62</v>
       </c>
@@ -18229,7 +18208,7 @@
         <v>3.9918290000000002E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="6">
         <v>63</v>
       </c>
@@ -18381,7 +18360,7 @@
         <v>3.7733380000000004E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="6">
         <v>64</v>
       </c>
@@ -18533,7 +18512,7 @@
         <v>4.260179E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="6">
         <v>65</v>
       </c>
@@ -18685,7 +18664,7 @@
         <v>4.1939197999999997E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="6">
         <v>66</v>
       </c>
@@ -18837,7 +18816,7 @@
         <v>4.9143251466666656E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="6">
         <v>67</v>
       </c>
@@ -18989,7 +18968,7 @@
         <v>5.6347304933333328E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="6">
         <v>68</v>
       </c>
@@ -19141,7 +19120,7 @@
         <v>6.355135839999998E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A55" s="6">
         <v>69</v>
       </c>
@@ -19293,7 +19272,7 @@
         <v>7.0755411866666659E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A56" s="6">
         <v>70</v>
       </c>
@@ -19445,7 +19424,7 @@
         <v>7.7959465333333339E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A57" s="6">
         <v>71</v>
       </c>
@@ -19597,7 +19576,7 @@
         <v>8.5163518799999977E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A58" s="6">
         <v>72</v>
       </c>
@@ -19749,7 +19728,7 @@
         <v>9.2367572266666642E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A59" s="6">
         <v>73</v>
       </c>
@@ -19901,7 +19880,7 @@
         <v>9.9571625733333335E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A60" s="6">
         <v>74</v>
       </c>
@@ -20053,7 +20032,7 @@
         <v>0.1067756792</v>
       </c>
     </row>
-    <row r="61" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A61" s="6">
         <v>75</v>
       </c>
@@ -20205,7 +20184,7 @@
         <v>0.11397973266666664</v>
       </c>
     </row>
-    <row r="62" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A62" s="6">
         <v>76</v>
       </c>
@@ -20357,7 +20336,7 @@
         <v>0.12118378613333332</v>
       </c>
     </row>
-    <row r="63" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A63" s="6">
         <v>77</v>
       </c>
@@ -20509,7 +20488,7 @@
         <v>0.12838783959999994</v>
       </c>
     </row>
-    <row r="64" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A64" s="6">
         <v>78</v>
       </c>
@@ -20661,7 +20640,7 @@
         <v>0.13559189306666666</v>
       </c>
     </row>
-    <row r="65" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A65" s="6">
         <v>79</v>
       </c>
@@ -20813,7 +20792,7 @@
         <v>0.14279594653333333</v>
       </c>
     </row>
-    <row r="66" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A66" s="6">
         <v>80</v>
       </c>
@@ -20972,14 +20951,14 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36656541-FCAB-471F-B3CC-C2331CBC317D}">
-  <dimension ref="A1:CL66"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AX66"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="8.85546875" style="4"/>
-    <col min="5" max="16384" width="8.85546875" style="5"/>
+    <col min="1" max="4" width="8.81640625" style="4"/>
+    <col min="5" max="16384" width="8.81640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:90" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
@@ -21130,24 +21109,8 @@
       <c r="AX1" s="4">
         <v>2024</v>
       </c>
-      <c r="AY1" s="4"/>
-      <c r="AZ1" s="4"/>
-      <c r="BA1" s="4"/>
-      <c r="BB1" s="4"/>
-      <c r="BC1" s="4"/>
-      <c r="BD1" s="4"/>
-      <c r="BE1" s="4"/>
-      <c r="BF1" s="4"/>
-      <c r="BG1" s="4"/>
-      <c r="BH1" s="4"/>
-      <c r="BI1" s="4"/>
-      <c r="BJ1" s="4"/>
-      <c r="BK1" s="4"/>
-      <c r="BL1" s="4"/>
-      <c r="BM1" s="4"/>
-      <c r="BN1" s="4"/>
     </row>
-    <row r="2" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="6">
         <v>16</v>
       </c>
@@ -21298,10 +21261,8 @@
       <c r="AX2" s="5">
         <v>0.26019811999999998</v>
       </c>
-      <c r="AY2"/>
-      <c r="AZ2"/>
     </row>
-    <row r="3" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>17</v>
       </c>
@@ -21452,10 +21413,8 @@
       <c r="AX3" s="5">
         <v>0.18180854000000002</v>
       </c>
-      <c r="AY3"/>
-      <c r="AZ3"/>
     </row>
-    <row r="4" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
         <v>18</v>
       </c>
@@ -21606,10 +21565,8 @@
       <c r="AX4" s="5">
         <v>0.14871978999999996</v>
       </c>
-      <c r="AY4"/>
-      <c r="AZ4"/>
     </row>
-    <row r="5" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
         <v>19</v>
       </c>
@@ -21760,10 +21717,8 @@
       <c r="AX5" s="5">
         <v>0.14520216999999999</v>
       </c>
-      <c r="AY5"/>
-      <c r="AZ5"/>
     </row>
-    <row r="6" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <v>20</v>
       </c>
@@ -21914,10 +21869,8 @@
       <c r="AX6" s="5">
         <v>9.8097610000000016E-2</v>
       </c>
-      <c r="AY6"/>
-      <c r="AZ6"/>
     </row>
-    <row r="7" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>21</v>
       </c>
@@ -22068,10 +22021,8 @@
       <c r="AX7" s="5">
         <v>8.9078409999999997E-2</v>
       </c>
-      <c r="AY7"/>
-      <c r="AZ7"/>
     </row>
-    <row r="8" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <v>22</v>
       </c>
@@ -22222,10 +22173,8 @@
       <c r="AX8" s="5">
         <v>8.8558600000000001E-2</v>
       </c>
-      <c r="AY8"/>
-      <c r="AZ8"/>
     </row>
-    <row r="9" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>23</v>
       </c>
@@ -22376,11 +22325,8 @@
       <c r="AX9" s="5">
         <v>5.0640470000000007E-2</v>
       </c>
-      <c r="AY9"/>
-      <c r="AZ9"/>
-      <c r="CL9" s="7"/>
     </row>
-    <row r="10" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>24</v>
       </c>
@@ -22531,11 +22477,8 @@
       <c r="AX10" s="5">
         <v>4.37875E-2</v>
       </c>
-      <c r="AY10"/>
-      <c r="AZ10"/>
-      <c r="CL10" s="7"/>
     </row>
-    <row r="11" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
         <v>25</v>
       </c>
@@ -22686,11 +22629,8 @@
       <c r="AX11" s="5">
         <v>3.5014460000000004E-2</v>
       </c>
-      <c r="AY11"/>
-      <c r="AZ11"/>
-      <c r="CL11" s="7"/>
     </row>
-    <row r="12" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" s="6">
         <v>26</v>
       </c>
@@ -22841,11 +22781,8 @@
       <c r="AX12" s="5">
         <v>2.1639590000000004E-2</v>
       </c>
-      <c r="AY12"/>
-      <c r="AZ12"/>
-      <c r="CL12" s="7"/>
     </row>
-    <row r="13" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
         <v>27</v>
       </c>
@@ -22996,11 +22933,8 @@
       <c r="AX13" s="5">
         <v>2.6975739999999998E-2</v>
       </c>
-      <c r="AY13"/>
-      <c r="AZ13"/>
-      <c r="CL13" s="7"/>
     </row>
-    <row r="14" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="6">
         <v>28</v>
       </c>
@@ -23151,11 +23085,8 @@
       <c r="AX14" s="5">
         <v>3.2589880000000002E-2</v>
       </c>
-      <c r="AY14"/>
-      <c r="AZ14"/>
-      <c r="CL14" s="7"/>
     </row>
-    <row r="15" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="6">
         <v>29</v>
       </c>
@@ -23306,11 +23237,8 @@
       <c r="AX15" s="5">
         <v>1.9616940000000003E-2</v>
       </c>
-      <c r="AY15"/>
-      <c r="AZ15"/>
-      <c r="CL15" s="7"/>
     </row>
-    <row r="16" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="6">
         <v>30</v>
       </c>
@@ -23461,11 +23389,8 @@
       <c r="AX16" s="5">
         <v>2.8011589999999996E-2</v>
       </c>
-      <c r="AY16"/>
-      <c r="AZ16"/>
-      <c r="CL16" s="7"/>
     </row>
-    <row r="17" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="6">
         <v>31</v>
       </c>
@@ -23616,11 +23541,8 @@
       <c r="AX17" s="5">
         <v>2.2562310000000002E-2</v>
       </c>
-      <c r="AY17"/>
-      <c r="AZ17"/>
-      <c r="CL17" s="7"/>
     </row>
-    <row r="18" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="6">
         <v>32</v>
       </c>
@@ -23771,11 +23693,8 @@
       <c r="AX18" s="5">
         <v>2.8440979999999998E-2</v>
       </c>
-      <c r="AY18"/>
-      <c r="AZ18"/>
-      <c r="CL18" s="7"/>
     </row>
-    <row r="19" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="6">
         <v>33</v>
       </c>
@@ -23926,11 +23845,8 @@
       <c r="AX19" s="5">
         <v>2.2318650000000002E-2</v>
       </c>
-      <c r="AY19"/>
-      <c r="AZ19"/>
-      <c r="CL19" s="7"/>
     </row>
-    <row r="20" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="6">
         <v>34</v>
       </c>
@@ -24081,11 +23997,8 @@
       <c r="AX20" s="5">
         <v>2.2305889999999998E-2</v>
       </c>
-      <c r="AY20"/>
-      <c r="AZ20"/>
-      <c r="CL20" s="7"/>
     </row>
-    <row r="21" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="6">
         <v>35</v>
       </c>
@@ -24236,11 +24149,8 @@
       <c r="AX21" s="5">
         <v>2.1616710000000001E-2</v>
       </c>
-      <c r="AY21"/>
-      <c r="AZ21"/>
-      <c r="CL21" s="7"/>
     </row>
-    <row r="22" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="6">
         <v>36</v>
       </c>
@@ -24391,11 +24301,8 @@
       <c r="AX22" s="5">
         <v>1.7932989999999999E-2</v>
       </c>
-      <c r="AY22"/>
-      <c r="AZ22"/>
-      <c r="CL22" s="7"/>
     </row>
-    <row r="23" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" s="6">
         <v>37</v>
       </c>
@@ -24546,11 +24453,8 @@
       <c r="AX23" s="5">
         <v>1.9648470000000001E-2</v>
       </c>
-      <c r="AY23"/>
-      <c r="AZ23"/>
-      <c r="CL23" s="7"/>
     </row>
-    <row r="24" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="6">
         <v>38</v>
       </c>
@@ -24701,11 +24605,8 @@
       <c r="AX24" s="5">
         <v>2.0679350000000006E-2</v>
       </c>
-      <c r="AY24"/>
-      <c r="AZ24"/>
-      <c r="CL24" s="7"/>
     </row>
-    <row r="25" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="6">
         <v>39</v>
       </c>
@@ -24856,11 +24757,8 @@
       <c r="AX25" s="5">
         <v>2.6637729999999998E-2</v>
       </c>
-      <c r="AY25"/>
-      <c r="AZ25"/>
-      <c r="CL25" s="7"/>
     </row>
-    <row r="26" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="6">
         <v>40</v>
       </c>
@@ -25011,11 +24909,8 @@
       <c r="AX26" s="5">
         <v>1.9886649999999999E-2</v>
       </c>
-      <c r="AY26"/>
-      <c r="AZ26"/>
-      <c r="CL26" s="7"/>
     </row>
-    <row r="27" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="6">
         <v>41</v>
       </c>
@@ -25166,11 +25061,8 @@
       <c r="AX27" s="5">
         <v>1.955728E-2</v>
       </c>
-      <c r="AY27"/>
-      <c r="AZ27"/>
-      <c r="CL27" s="7"/>
     </row>
-    <row r="28" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="6">
         <v>42</v>
       </c>
@@ -25321,11 +25213,8 @@
       <c r="AX28" s="5">
         <v>2.2265529999999999E-2</v>
       </c>
-      <c r="AY28"/>
-      <c r="AZ28"/>
-      <c r="CL28" s="7"/>
     </row>
-    <row r="29" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="6">
         <v>43</v>
       </c>
@@ -25476,11 +25365,8 @@
       <c r="AX29" s="5">
         <v>2.2124769999999998E-2</v>
       </c>
-      <c r="AY29"/>
-      <c r="AZ29"/>
-      <c r="CL29" s="7"/>
     </row>
-    <row r="30" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="6">
         <v>44</v>
       </c>
@@ -25631,11 +25517,8 @@
       <c r="AX30" s="5">
         <v>2.075113E-2</v>
       </c>
-      <c r="AY30"/>
-      <c r="AZ30"/>
-      <c r="CL30" s="7"/>
     </row>
-    <row r="31" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="6">
         <v>45</v>
       </c>
@@ -25786,11 +25669,8 @@
       <c r="AX31" s="5">
         <v>1.851042E-2</v>
       </c>
-      <c r="AY31"/>
-      <c r="AZ31"/>
-      <c r="CL31" s="7"/>
     </row>
-    <row r="32" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A32" s="6">
         <v>46</v>
       </c>
@@ -25941,11 +25821,8 @@
       <c r="AX32" s="5">
         <v>2.3261609999999999E-2</v>
       </c>
-      <c r="AY32"/>
-      <c r="AZ32"/>
-      <c r="CL32" s="7"/>
     </row>
-    <row r="33" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="6">
         <v>47</v>
       </c>
@@ -26096,11 +25973,8 @@
       <c r="AX33" s="5">
         <v>3.0736720000000006E-2</v>
       </c>
-      <c r="AY33"/>
-      <c r="AZ33"/>
-      <c r="CL33" s="7"/>
     </row>
-    <row r="34" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="6">
         <v>48</v>
       </c>
@@ -26251,11 +26125,8 @@
       <c r="AX34" s="5">
         <v>1.7331159999999998E-2</v>
       </c>
-      <c r="AY34"/>
-      <c r="AZ34"/>
-      <c r="CL34" s="7"/>
     </row>
-    <row r="35" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="6">
         <v>49</v>
       </c>
@@ -26406,11 +26277,8 @@
       <c r="AX35" s="5">
         <v>2.0583360000000002E-2</v>
       </c>
-      <c r="AY35"/>
-      <c r="AZ35"/>
-      <c r="CL35" s="7"/>
     </row>
-    <row r="36" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="6">
         <v>50</v>
       </c>
@@ -26561,11 +26429,8 @@
       <c r="AX36" s="5">
         <v>1.68921E-2</v>
       </c>
-      <c r="AY36"/>
-      <c r="AZ36"/>
-      <c r="CL36" s="7"/>
     </row>
-    <row r="37" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="6">
         <v>51</v>
       </c>
@@ -26716,11 +26581,8 @@
       <c r="AX37" s="5">
         <v>1.2943199999999998E-2</v>
       </c>
-      <c r="AY37"/>
-      <c r="AZ37"/>
-      <c r="CL37" s="7"/>
     </row>
-    <row r="38" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="6">
         <v>52</v>
       </c>
@@ -26871,11 +26733,8 @@
       <c r="AX38" s="5">
         <v>1.6397169999999999E-2</v>
       </c>
-      <c r="AY38"/>
-      <c r="AZ38"/>
-      <c r="CL38" s="7"/>
     </row>
-    <row r="39" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="6">
         <v>53</v>
       </c>
@@ -27026,11 +26885,8 @@
       <c r="AX39" s="5">
         <v>2.2326510000000001E-2</v>
       </c>
-      <c r="AY39"/>
-      <c r="AZ39"/>
-      <c r="CL39" s="7"/>
     </row>
-    <row r="40" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="6">
         <v>54</v>
       </c>
@@ -27181,11 +27037,8 @@
       <c r="AX40" s="5">
         <v>1.9069510000000001E-2</v>
       </c>
-      <c r="AY40"/>
-      <c r="AZ40"/>
-      <c r="CL40" s="7"/>
     </row>
-    <row r="41" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="6">
         <v>55</v>
       </c>
@@ -27336,11 +27189,8 @@
       <c r="AX41" s="5">
         <v>2.4882430000000001E-2</v>
       </c>
-      <c r="AY41"/>
-      <c r="AZ41"/>
-      <c r="CL41" s="7"/>
     </row>
-    <row r="42" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="6">
         <v>56</v>
       </c>
@@ -27491,11 +27341,8 @@
       <c r="AX42" s="5">
         <v>2.275458E-2</v>
       </c>
-      <c r="AY42"/>
-      <c r="AZ42"/>
-      <c r="CL42" s="7"/>
     </row>
-    <row r="43" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="6">
         <v>57</v>
       </c>
@@ -27646,11 +27493,8 @@
       <c r="AX43" s="5">
         <v>1.7978999999999998E-2</v>
       </c>
-      <c r="AY43"/>
-      <c r="AZ43"/>
-      <c r="CL43" s="7"/>
     </row>
-    <row r="44" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A44" s="6">
         <v>58</v>
       </c>
@@ -27801,11 +27645,8 @@
       <c r="AX44" s="5">
         <v>2.0993350000000001E-2</v>
       </c>
-      <c r="AY44"/>
-      <c r="AZ44"/>
-      <c r="CL44" s="7"/>
     </row>
-    <row r="45" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="6">
         <v>59</v>
       </c>
@@ -27956,11 +27797,8 @@
       <c r="AX45" s="5">
         <v>1.9619069999999995E-2</v>
       </c>
-      <c r="AY45"/>
-      <c r="AZ45"/>
-      <c r="CL45" s="7"/>
     </row>
-    <row r="46" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="6">
         <v>60</v>
       </c>
@@ -28111,11 +27949,8 @@
       <c r="AX46" s="5">
         <v>2.1355597999999996E-2</v>
       </c>
-      <c r="AY46"/>
-      <c r="AZ46"/>
-      <c r="CL46" s="7"/>
     </row>
-    <row r="47" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="6">
         <v>61</v>
       </c>
@@ -28266,9 +28101,8 @@
       <c r="AX47" s="5">
         <v>2.77878181E-2</v>
       </c>
-      <c r="CL47" s="7"/>
     </row>
-    <row r="48" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A48" s="6">
         <v>62</v>
       </c>
@@ -28419,9 +28253,8 @@
       <c r="AX48" s="5">
         <v>3.422003819999999E-2</v>
       </c>
-      <c r="CL48" s="7"/>
     </row>
-    <row r="49" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="6">
         <v>63</v>
       </c>
@@ -28572,9 +28405,8 @@
       <c r="AX49" s="5">
         <v>4.0652258300000001E-2</v>
       </c>
-      <c r="CL49" s="7"/>
     </row>
-    <row r="50" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="6">
         <v>64</v>
       </c>
@@ -28725,9 +28557,8 @@
       <c r="AX50" s="5">
         <v>4.7084478400000004E-2</v>
       </c>
-      <c r="CL50" s="7"/>
     </row>
-    <row r="51" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="6">
         <v>65</v>
       </c>
@@ -28878,9 +28709,8 @@
       <c r="AX51" s="5">
         <v>5.3516698500000001E-2</v>
       </c>
-      <c r="CL51" s="7"/>
     </row>
-    <row r="52" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="6">
         <v>66</v>
       </c>
@@ -29031,9 +28861,8 @@
       <c r="AX52" s="5">
         <v>5.9948918599999991E-2</v>
       </c>
-      <c r="CL52" s="7"/>
     </row>
-    <row r="53" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="6">
         <v>67</v>
       </c>
@@ -29184,9 +29013,8 @@
       <c r="AX53" s="5">
         <v>6.6381138699999995E-2</v>
       </c>
-      <c r="CL53" s="7"/>
     </row>
-    <row r="54" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="6">
         <v>68</v>
       </c>
@@ -29337,9 +29165,8 @@
       <c r="AX54" s="5">
         <v>7.2813358800000005E-2</v>
       </c>
-      <c r="CL54" s="7"/>
     </row>
-    <row r="55" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A55" s="6">
         <v>69</v>
       </c>
@@ -29490,9 +29317,8 @@
       <c r="AX55" s="5">
         <v>7.9245578900000002E-2</v>
       </c>
-      <c r="CL55" s="7"/>
     </row>
-    <row r="56" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A56" s="6">
         <v>70</v>
       </c>
@@ -29643,9 +29469,8 @@
       <c r="AX56" s="5">
         <v>8.5677798999999999E-2</v>
       </c>
-      <c r="CL56" s="7"/>
     </row>
-    <row r="57" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A57" s="6">
         <v>71</v>
       </c>
@@ -29796,9 +29621,8 @@
       <c r="AX57" s="5">
         <v>9.211001910000001E-2</v>
       </c>
-      <c r="CL57" s="7"/>
     </row>
-    <row r="58" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A58" s="6">
         <v>72</v>
       </c>
@@ -29950,7 +29774,7 @@
         <v>9.8542239199999992E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A59" s="6">
         <v>73</v>
       </c>
@@ -30102,7 +29926,7 @@
         <v>0.1049744593</v>
       </c>
     </row>
-    <row r="60" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A60" s="6">
         <v>74</v>
       </c>
@@ -30254,7 +30078,7 @@
         <v>0.11140667940000001</v>
       </c>
     </row>
-    <row r="61" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A61" s="6">
         <v>75</v>
       </c>
@@ -30406,7 +30230,7 @@
         <v>0.1178388995</v>
       </c>
     </row>
-    <row r="62" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A62" s="6">
         <v>76</v>
       </c>
@@ -30558,7 +30382,7 @@
         <v>0.12427111960000001</v>
       </c>
     </row>
-    <row r="63" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A63" s="6">
         <v>77</v>
       </c>
@@ -30710,7 +30534,7 @@
         <v>0.13070333969999998</v>
       </c>
     </row>
-    <row r="64" spans="1:90" ht="15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A64" s="6">
         <v>78</v>
       </c>
@@ -30862,7 +30686,7 @@
         <v>0.1371355598</v>
       </c>
     </row>
-    <row r="65" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A65" s="6">
         <v>79</v>
       </c>
@@ -31014,7 +30838,7 @@
         <v>0.1435677799</v>
       </c>
     </row>
-    <row r="66" spans="1:50" ht="15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A66" s="6">
         <v>80</v>
       </c>
@@ -31174,9 +30998,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E2C5941-0F60-4C3F-9BA6-C77841CC7AAE}">
   <dimension ref="A1:AX66"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
@@ -31328,7 +31152,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A2" s="6">
         <v>16</v>
       </c>
@@ -31480,7 +31304,7 @@
         <v>0.26019811999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>17</v>
       </c>
@@ -31632,7 +31456,7 @@
         <v>0.18180854000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
         <v>18</v>
       </c>
@@ -31784,7 +31608,7 @@
         <v>0.14871978999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
         <v>19</v>
       </c>
@@ -31936,7 +31760,7 @@
         <v>0.14520216999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <v>20</v>
       </c>
@@ -32088,7 +31912,7 @@
         <v>9.8097610000000016E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>21</v>
       </c>
@@ -32240,7 +32064,7 @@
         <v>8.9078409999999997E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <v>22</v>
       </c>
@@ -32392,7 +32216,7 @@
         <v>8.8558600000000001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>23</v>
       </c>
@@ -32544,7 +32368,7 @@
         <v>6.745232000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>24</v>
       </c>
@@ -32696,7 +32520,7 @@
         <v>5.5023500000000003E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
         <v>25</v>
       </c>
@@ -32848,7 +32672,7 @@
         <v>5.0879679999999997E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A12" s="6">
         <v>26</v>
       </c>
@@ -33000,7 +32824,7 @@
         <v>4.0940579999999997E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
         <v>27</v>
       </c>
@@ -33152,7 +32976,7 @@
         <v>4.0392439999999995E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A14" s="6">
         <v>28</v>
       </c>
@@ -33304,7 +33128,7 @@
         <v>4.8918830000000003E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A15" s="6">
         <v>29</v>
       </c>
@@ -33456,7 +33280,7 @@
         <v>3.957198E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A16" s="6">
         <v>30</v>
       </c>
@@ -33608,7 +33432,7 @@
         <v>4.2480329999999997E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A17" s="6">
         <v>31</v>
       </c>
@@ -33760,7 +33584,7 @@
         <v>3.3808650000000003E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A18" s="6">
         <v>32</v>
       </c>
@@ -33912,7 +33736,7 @@
         <v>4.0517319999999996E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A19" s="6">
         <v>33</v>
       </c>
@@ -34064,7 +33888,7 @@
         <v>3.591602E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A20" s="6">
         <v>34</v>
       </c>
@@ -34216,7 +34040,7 @@
         <v>3.6668350000000002E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A21" s="6">
         <v>35</v>
       </c>
@@ -34368,7 +34192,7 @@
         <v>3.8220319999999995E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A22" s="6">
         <v>36</v>
       </c>
@@ -34520,7 +34344,7 @@
         <v>2.8513329999999996E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A23" s="6">
         <v>37</v>
       </c>
@@ -34672,7 +34496,7 @@
         <v>3.1724290000000002E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A24" s="6">
         <v>38</v>
       </c>
@@ -34824,7 +34648,7 @@
         <v>2.9454850000000005E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A25" s="6">
         <v>39</v>
       </c>
@@ -34976,7 +34800,7 @@
         <v>3.7669190000000005E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A26" s="6">
         <v>40</v>
       </c>
@@ -35128,7 +34952,7 @@
         <v>3.0450950000000004E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A27" s="6">
         <v>41</v>
       </c>
@@ -35280,7 +35104,7 @@
         <v>3.1953229999999999E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A28" s="6">
         <v>42</v>
       </c>
@@ -35432,7 +35256,7 @@
         <v>3.1920499999999997E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A29" s="6">
         <v>43</v>
       </c>
@@ -35584,7 +35408,7 @@
         <v>3.1741510000000001E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A30" s="6">
         <v>44</v>
       </c>
@@ -35736,7 +35560,7 @@
         <v>3.3504269999999996E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A31" s="6">
         <v>45</v>
       </c>
@@ -35888,7 +35712,7 @@
         <v>3.0541649999999997E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A32" s="6">
         <v>46</v>
       </c>
@@ -36040,7 +35864,7 @@
         <v>3.1189939999999999E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A33" s="6">
         <v>47</v>
       </c>
@@ -36192,7 +36016,7 @@
         <v>3.5657000000000001E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A34" s="6">
         <v>48</v>
       </c>
@@ -36344,7 +36168,7 @@
         <v>2.8557769999999993E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A35" s="6">
         <v>49</v>
       </c>
@@ -36496,7 +36320,7 @@
         <v>2.6860820000000001E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A36" s="6">
         <v>50</v>
       </c>
@@ -36648,7 +36472,7 @@
         <v>2.3105970000000003E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A37" s="6">
         <v>51</v>
       </c>
@@ -36800,7 +36624,7 @@
         <v>2.7923969999999999E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A38" s="6">
         <v>52</v>
       </c>
@@ -36952,7 +36776,7 @@
         <v>2.3828380000000003E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A39" s="6">
         <v>53</v>
       </c>
@@ -37104,7 +36928,7 @@
         <v>2.4713160000000001E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A40" s="6">
         <v>54</v>
       </c>
@@ -37256,7 +37080,7 @@
         <v>2.369959E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A41" s="6">
         <v>55</v>
       </c>
@@ -37408,7 +37232,7 @@
         <v>2.7680859999999995E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A42" s="6">
         <v>56</v>
       </c>
@@ -37560,7 +37384,7 @@
         <v>2.7324529999999996E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A43" s="6">
         <v>57</v>
       </c>
@@ -37712,7 +37536,7 @@
         <v>2.3671579999999998E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A44" s="6">
         <v>58</v>
       </c>
@@ -37864,7 +37688,7 @@
         <v>2.8590329999999997E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A45" s="6">
         <v>59</v>
       </c>
@@ -38016,7 +37840,7 @@
         <v>2.8783280000000001E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A46" s="6">
         <v>60</v>
       </c>
@@ -38168,7 +37992,7 @@
         <v>3.0878620000000002E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A47" s="6">
         <v>61</v>
       </c>
@@ -38320,7 +38144,7 @@
         <v>3.6834689000000004E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A48" s="6">
         <v>62</v>
       </c>
@@ -38472,7 +38296,7 @@
         <v>4.2790757999999998E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A49" s="6">
         <v>63</v>
       </c>
@@ -38624,7 +38448,7 @@
         <v>4.8746827E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A50" s="6">
         <v>64</v>
       </c>
@@ -38776,7 +38600,7 @@
         <v>5.4702896000000001E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A51" s="6">
         <v>65</v>
       </c>
@@ -38928,7 +38752,7 @@
         <v>6.0658965000000009E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A52" s="6">
         <v>66</v>
       </c>
@@ -39080,7 +38904,7 @@
         <v>6.661503399999999E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A53" s="6">
         <v>67</v>
       </c>
@@ -39232,7 +39056,7 @@
         <v>7.2571102999999998E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A54" s="6">
         <v>68</v>
       </c>
@@ -39384,7 +39208,7 @@
         <v>7.8527172000000006E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A55" s="6">
         <v>69</v>
       </c>
@@ -39536,7 +39360,7 @@
         <v>8.4483241000000001E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A56" s="6">
         <v>70</v>
       </c>
@@ -39688,7 +39512,7 @@
         <v>9.0439310000000009E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A57" s="6">
         <v>71</v>
       </c>
@@ -39840,7 +39664,7 @@
         <v>9.6395379000000017E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A58" s="6">
         <v>72</v>
       </c>
@@ -39992,7 +39816,7 @@
         <v>0.102351448</v>
       </c>
     </row>
-    <row r="59" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A59" s="6">
         <v>73</v>
       </c>
@@ -40144,7 +39968,7 @@
         <v>0.10830751699999999</v>
       </c>
     </row>
-    <row r="60" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A60" s="6">
         <v>74</v>
       </c>
@@ -40296,7 +40120,7 @@
         <v>0.114263586</v>
       </c>
     </row>
-    <row r="61" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A61" s="6">
         <v>75</v>
       </c>
@@ -40448,7 +40272,7 @@
         <v>0.12021965500000002</v>
       </c>
     </row>
-    <row r="62" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A62" s="6">
         <v>76</v>
       </c>
@@ -40600,7 +40424,7 @@
         <v>0.12617572400000002</v>
       </c>
     </row>
-    <row r="63" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A63" s="6">
         <v>77</v>
       </c>
@@ -40752,7 +40576,7 @@
         <v>0.13213179300000003</v>
       </c>
     </row>
-    <row r="64" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A64" s="6">
         <v>78</v>
       </c>
@@ -40904,7 +40728,7 @@
         <v>0.13808786200000003</v>
       </c>
     </row>
-    <row r="65" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A65" s="6">
         <v>79</v>
       </c>
@@ -41056,7 +40880,7 @@
         <v>0.14404393100000004</v>
       </c>
     </row>
-    <row r="66" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:50" x14ac:dyDescent="0.35">
       <c r="A66" s="6">
         <v>80</v>
       </c>
@@ -41216,9 +41040,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B31A884-F39B-4D2D-93E0-D88DBF495E2F}">
   <dimension ref="A1:T19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>61</v>
       </c>
@@ -41280,11 +41104,11 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="19">
+      <c r="B2" s="18">
         <v>3.3220039193875528</v>
       </c>
       <c r="C2">
@@ -41342,11 +41166,11 @@
         <v>-3.5416304283025245E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="19">
+      <c r="B3" s="18">
         <v>-0.28014931706682594</v>
       </c>
       <c r="C3">
@@ -41404,11 +41228,11 @@
         <v>-0.14885284238427224</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="18">
         <v>-0.19877766854638357</v>
       </c>
       <c r="C4">
@@ -41466,11 +41290,11 @@
         <v>-0.14903612693976501</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="18">
         <v>-0.42384157126915017</v>
       </c>
       <c r="C5">
@@ -41528,11 +41352,11 @@
         <v>-0.1488505184012999</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A6" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="18">
         <v>-0.38394364531610237</v>
       </c>
       <c r="C6">
@@ -41590,11 +41414,11 @@
         <v>-0.14876549571684003</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="18">
         <v>1.5171954960451808</v>
       </c>
       <c r="C7">
@@ -41652,11 +41476,11 @@
         <v>-2.7898746371138178E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A8" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="18">
         <v>-6.4610856082136625E-2</v>
       </c>
       <c r="C8">
@@ -41714,11 +41538,11 @@
         <v>-1.3372169426667689E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A9" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="18">
         <v>-0.15974223353976583</v>
       </c>
       <c r="C9">
@@ -41776,11 +41600,11 @@
         <v>-1.0928944726124046E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A10" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="18">
         <v>-6.3536962200238786E-2</v>
       </c>
       <c r="C10">
@@ -41838,11 +41662,11 @@
         <v>-1.083806253243007E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A11" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="18">
         <v>-0.30775426382312232</v>
       </c>
       <c r="C11">
@@ -41900,11 +41724,11 @@
         <v>-1.0932388016875905E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A12" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="18">
         <v>-0.15162850249887386</v>
       </c>
       <c r="C12">
@@ -41962,11 +41786,11 @@
         <v>-1.0672934281322143E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A13" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="18">
         <v>-3.7317922791812561E-3</v>
       </c>
       <c r="C13">
@@ -42024,11 +41848,11 @@
         <v>-1.1843326275247906E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A14" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="18">
         <v>-5.4183327711139016E-3</v>
       </c>
       <c r="C14">
@@ -42086,11 +41910,11 @@
         <v>-1.0244321912134775E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A15" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="18">
         <v>-0.49765802607006887</v>
       </c>
       <c r="C15">
@@ -42148,11 +41972,11 @@
         <v>-1.0319993005708817E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A16" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="18">
         <v>-6.9823297500294743E-2</v>
       </c>
       <c r="C16">
@@ -42210,11 +42034,11 @@
         <v>-1.1885693202050004E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A17" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="18">
         <v>-0.20489121093656346</v>
       </c>
       <c r="C17">
@@ -42272,11 +42096,11 @@
         <v>-1.1455520606228623E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A18" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="18">
         <v>-0.51920158172421094</v>
       </c>
       <c r="C18">
@@ -42334,11 +42158,11 @@
         <v>-1.0293612120358798E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A19" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="18">
         <v>-1.7618049762229764</v>
       </c>
       <c r="C19">
@@ -42404,9 +42228,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8FA253C-38A9-483B-BC7F-FF4D6A7E64FE}">
   <dimension ref="A1:T19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>61</v>
       </c>
@@ -42468,11 +42292,11 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="19">
+      <c r="B2" s="18">
         <v>1.9220710453212315</v>
       </c>
       <c r="C2">
@@ -42530,11 +42354,11 @@
         <v>-3.5443995150077267E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="19">
+      <c r="B3" s="18">
         <v>7.3598916060736888E-2</v>
       </c>
       <c r="C3">
@@ -42592,11 +42416,11 @@
         <v>-8.4109512923886201E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="18">
         <v>1.8977610924120047E-2</v>
       </c>
       <c r="C4">
@@ -42654,11 +42478,11 @@
         <v>-8.4687050220290556E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="18">
         <v>-0.12412062488765985</v>
       </c>
       <c r="C5">
@@ -42716,11 +42540,11 @@
         <v>-8.6352108125011956E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A6" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="18">
         <v>-0.11360011656508247</v>
       </c>
       <c r="C6">
@@ -42778,11 +42602,11 @@
         <v>-8.3725315998750289E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="18">
         <v>1.832838053376479</v>
       </c>
       <c r="C7">
@@ -42840,11 +42664,11 @@
         <v>-1.1878865375397826E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A8" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="18">
         <v>5.5349903818609388E-2</v>
       </c>
       <c r="C8">
@@ -42902,11 +42726,11 @@
         <v>-4.625211430212983E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A9" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="18">
         <v>9.3226009408149454E-3</v>
       </c>
       <c r="C9">
@@ -42964,11 +42788,11 @@
         <v>-4.6079895815085634E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A10" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="18">
         <v>-8.0419910063983621E-2</v>
       </c>
       <c r="C10">
@@ -43026,11 +42850,11 @@
         <v>-4.3138027375580488E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A11" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="18">
         <v>-1.9808186534610195E-2</v>
       </c>
       <c r="C11">
@@ -43088,11 +42912,11 @@
         <v>-4.157398398245484E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A12" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="18">
         <v>-8.27981408125429E-2</v>
       </c>
       <c r="C12">
@@ -43150,11 +42974,11 @@
         <v>-4.2006316563503454E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A13" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="18">
         <v>-8.6401271925290818E-2</v>
       </c>
       <c r="C13">
@@ -43212,11 +43036,11 @@
         <v>-4.6378269229101184E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A14" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="18">
         <v>-0.19490393303561573</v>
       </c>
       <c r="C14">
@@ -43274,11 +43098,11 @@
         <v>-4.4640337855897348E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A15" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="18">
         <v>-0.23719661875889966</v>
       </c>
       <c r="C15">
@@ -43336,11 +43160,11 @@
         <v>-4.3047756070677696E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A16" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="18">
         <v>1.6127753782126325E-3</v>
       </c>
       <c r="C16">
@@ -43398,11 +43222,11 @@
         <v>-4.2685847954493936E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A17" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="18">
         <v>-8.8836692077451318E-2</v>
       </c>
       <c r="C17">
@@ -43460,11 +43284,11 @@
         <v>-4.4973015013057404E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A18" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="18">
         <v>-8.4288550485971225E-2</v>
       </c>
       <c r="C18">
@@ -43522,11 +43346,11 @@
         <v>-4.3900487142188183E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A19" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="18">
         <v>-1.9734041268446605</v>
       </c>
       <c r="C19">
@@ -43592,9 +43416,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE83AD0B-62F5-4A81-BCDC-3EC820E3DC16}">
   <dimension ref="A1:T19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>61</v>
       </c>
@@ -43656,11 +43480,11 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="19">
+      <c r="B2" s="18">
         <v>5.975311123373471</v>
       </c>
       <c r="C2">
@@ -43718,11 +43542,11 @@
         <v>-7.1613088912057851E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="19">
+      <c r="B3" s="18">
         <v>-0.24413111658645587</v>
       </c>
       <c r="C3">
@@ -43780,11 +43604,11 @@
         <v>-1.9526381793252119E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="18">
         <v>-0.58418104417849592</v>
       </c>
       <c r="C4">
@@ -43842,11 +43666,11 @@
         <v>-1.88822206336366E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="18">
         <v>-0.73888341891446052</v>
       </c>
       <c r="C5">
@@ -43904,11 +43728,11 @@
         <v>-1.8927494064318144E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A6" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="18">
         <v>-0.68960625064994885</v>
       </c>
       <c r="C6">
@@ -43966,11 +43790,11 @@
         <v>-1.9315815848071835E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="18">
         <v>0.99962566534652375</v>
       </c>
       <c r="C7">
@@ -44028,11 +43852,11 @@
         <v>-1.6565968080052413E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A8" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="18">
         <v>1.2578063180959748E-2</v>
       </c>
       <c r="C8">
@@ -44090,11 +43914,11 @@
         <v>-4.1902413783987194E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A9" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="18">
         <v>-0.2573137466624002</v>
       </c>
       <c r="C9">
@@ -44152,11 +43976,11 @@
         <v>-4.444529060319247E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A10" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="18">
         <v>-5.4468930786818137E-2</v>
       </c>
       <c r="C10">
@@ -44214,11 +44038,11 @@
         <v>-4.6917220426184961E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A11" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="18">
         <v>-5.10025056596791E-2</v>
       </c>
       <c r="C11">
@@ -44276,11 +44100,11 @@
         <v>-4.3920575431861328E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A12" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="18">
         <v>-0.3228758675310372</v>
       </c>
       <c r="C12">
@@ -44338,11 +44162,11 @@
         <v>-2.5272066550653602E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A13" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="18">
         <v>-0.12229887893727533</v>
       </c>
       <c r="C13">
@@ -44400,11 +44224,11 @@
         <v>-3.7694427074636896E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A14" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="18">
         <v>-0.19570143890896316</v>
       </c>
       <c r="C14">
@@ -44462,11 +44286,11 @@
         <v>-4.0636389562362174E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A15" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="18">
         <v>-0.2932466872478387</v>
       </c>
       <c r="C15">
@@ -44524,11 +44348,11 @@
         <v>-4.6529172380434117E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A16" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="18">
         <v>-9.80024829195945E-2</v>
       </c>
       <c r="C16">
@@ -44586,11 +44410,11 @@
         <v>-3.9940166814911053E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A17" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="18">
         <v>-0.23585854208658888</v>
       </c>
       <c r="C17">
@@ -44648,11 +44472,11 @@
         <v>-3.3260633146255346E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A18" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="18">
         <v>-2.148395583679014E-2</v>
       </c>
       <c r="C18">
@@ -44710,11 +44534,11 @@
         <v>-4.3689659654760479E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A19" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="18">
         <v>-1.6794537820929836</v>
       </c>
       <c r="C19">
@@ -44780,9 +44604,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{298225BB-FD6B-487D-8E0A-5B17245B7D37}">
   <dimension ref="A1:T19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>61</v>
       </c>
@@ -44844,11 +44668,11 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="19">
+      <c r="B2" s="18">
         <v>3.7763942488993747</v>
       </c>
       <c r="C2">
@@ -44906,11 +44730,11 @@
         <v>-8.0884031096164523E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="19">
+      <c r="B3" s="18">
         <v>-3.5162661886621031E-2</v>
       </c>
       <c r="C3">
@@ -44968,11 +44792,11 @@
         <v>-4.7159132329863641E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="18">
         <v>-0.26605157249639011</v>
       </c>
       <c r="C4">
@@ -45030,11 +44854,11 @@
         <v>-4.8747912666294397E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A5" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="18">
         <v>-0.38286734280983098</v>
       </c>
       <c r="C5">
@@ -45092,11 +44916,11 @@
         <v>-4.6445781622898585E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A6" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="18">
         <v>-0.34192199887615993</v>
       </c>
       <c r="C6">
@@ -45154,11 +44978,11 @@
         <v>-4.9030571989960624E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A7" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="18">
         <v>1.1644048313620481</v>
       </c>
       <c r="C7">
@@ -45216,11 +45040,11 @@
         <v>-6.736439180099811E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A8" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="18">
         <v>-5.3546122920729626E-2</v>
       </c>
       <c r="C8">
@@ -45278,11 +45102,11 @@
         <v>-2.7998613131418881E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A9" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="18">
         <v>-0.11467569244774736</v>
       </c>
       <c r="C9">
@@ -45340,11 +45164,11 @@
         <v>-2.7045184444692435E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A10" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="18">
         <v>-0.12112950549533991</v>
       </c>
       <c r="C10">
@@ -45402,11 +45226,11 @@
         <v>-2.7228858565888892E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A11" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="18">
         <v>-0.27748563767578366</v>
       </c>
       <c r="C11">
@@ -45464,11 +45288,11 @@
         <v>-2.6261043632189495E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A12" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="18">
         <v>-7.3163802889426602E-2</v>
       </c>
       <c r="C12">
@@ -45526,11 +45350,11 @@
         <v>-2.5854586257496267E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A13" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="18">
         <v>-0.35890032155550278</v>
       </c>
       <c r="C13">
@@ -45588,11 +45412,11 @@
         <v>-2.5922132986329867E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A14" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="18">
         <v>-0.28771624385775502</v>
       </c>
       <c r="C14">
@@ -45650,11 +45474,11 @@
         <v>-2.7112357921276072E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A15" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="18">
         <v>-0.39531177796844091</v>
       </c>
       <c r="C15">
@@ -45712,11 +45536,11 @@
         <v>-2.4417308246975724E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A16" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="18">
         <v>-0.18245339590242771</v>
       </c>
       <c r="C16">
@@ -45774,11 +45598,11 @@
         <v>-2.6761462165507013E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A17" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="18">
         <v>-5.7001561243006954E-2</v>
       </c>
       <c r="C17">
@@ -45836,11 +45660,11 @@
         <v>-2.6494193995736386E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A18" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="18">
         <v>-1.4297786670785708E-3</v>
       </c>
       <c r="C18">
@@ -45898,11 +45722,11 @@
         <v>-2.6607686203638042E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A19" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="18">
         <v>-1.8207438265889697</v>
       </c>
       <c r="C19">
@@ -45968,297 +45792,297 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D29755F-03F5-4832-BD4A-46B3397AFE2F}">
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="1" max="1" width="25.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="9" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="11">
         <v>3.3220040000000002</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="11">
         <v>1.201606</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="10"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="9"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <v>-0.28014929999999999</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="11">
         <v>0.39096510000000001</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <v>0.47399999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <v>-0.1987777</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="11">
         <v>0.38538450000000002</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <v>0.60599999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="11">
         <v>-0.42384159999999999</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="11">
         <v>0.38333230000000001</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <v>0.26900000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="11">
         <v>-0.3839436</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="11">
         <v>0.38603229999999999</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <v>0.32</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="11">
         <v>1.5171950000000001</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="11">
         <v>8.5161100000000003E-2</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="10"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="9"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>-6.4610899999999999E-2</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="11">
         <v>0.15470610000000001</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <v>0.67600000000000005</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="11">
         <v>-0.1597422</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="11">
         <v>0.121174</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <v>0.187</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="11">
         <v>-6.3536999999999996E-2</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="11">
         <v>0.1413353</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <v>0.65300000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="11">
         <v>-0.30775429999999998</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="11">
         <v>0.1571158</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <v>0.05</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="11">
         <v>-0.1516285</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="11">
         <v>0.14044200000000001</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="9">
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="11">
         <v>-3.7318E-3</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="11">
         <v>0.1514829</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="9">
         <v>0.98</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="11">
         <v>-5.4183E-3</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="11">
         <v>0.10261720000000001</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <v>0.95799999999999996</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="11">
         <v>-0.49765799999999999</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="11">
         <v>0.13691249999999999</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="11">
         <v>-6.9823300000000005E-2</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="11">
         <v>0.27667580000000003</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="9">
         <v>0.80100000000000005</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="11">
         <v>-0.2048912</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="11">
         <v>0.1580975</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="9">
         <v>0.19500000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="11">
         <v>-0.51920160000000004</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="11">
         <v>0.21671409999999999</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="9">
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="13">
         <v>-1.7618050000000001</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13">
         <v>0.39915440000000002</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -46266,7 +46090,7 @@
         <v>42528</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>41</v>
       </c>
@@ -46274,17 +46098,17 @@
         <v>3.6499999999999998E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="11" t="s">
+    <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="10">
         <v>0.20810000000000001</v>
       </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
     </row>
-    <row r="26" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -46293,330 +46117,330 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A03763CC-A86A-48D7-B741-040395EE32CB}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" customWidth="1"/>
+    <col min="1" max="1" width="25.7265625" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="9" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="11">
         <v>1.9220710000000001</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="11">
         <v>0.36276370000000002</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <v>0</v>
       </c>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="10"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="9"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <v>7.3598899999999995E-2</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="11">
         <v>0.1011314</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <v>0.46700000000000003</v>
       </c>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <v>1.8977600000000001E-2</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="11">
         <v>9.6676399999999996E-2</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <v>0.84399999999999997</v>
       </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="11">
         <v>-0.1241206</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="11">
         <v>9.7509700000000005E-2</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <v>0.20300000000000001</v>
       </c>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="11">
         <v>-0.1136001</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="11">
         <v>0.1065963</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <v>0.28699999999999998</v>
       </c>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="11">
         <v>1.832838</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="11">
         <v>4.2043200000000003E-2</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <v>0</v>
       </c>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="10"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="9"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>5.53499E-2</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="11">
         <v>9.8907300000000004E-2</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <v>0.57599999999999996</v>
       </c>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="11">
         <v>9.3226000000000003E-3</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="11">
         <v>8.6884699999999995E-2</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <v>0.91500000000000004</v>
       </c>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="11">
         <v>-8.0419900000000002E-2</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="11">
         <v>9.72523E-2</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <v>0.40799999999999997</v>
       </c>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="11">
         <v>-1.9808200000000002E-2</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="11">
         <v>8.6937700000000007E-2</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <v>0.82</v>
       </c>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="11">
         <v>-8.2798099999999999E-2</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="11">
         <v>9.21984E-2</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="9">
         <v>0.36899999999999999</v>
       </c>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="11">
         <v>-8.64013E-2</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="11">
         <v>8.9165999999999995E-2</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="9">
         <v>0.33300000000000002</v>
       </c>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="11">
         <v>-0.19490389999999999</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="11">
         <v>8.5807700000000001E-2</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <v>2.3E-2</v>
       </c>
-      <c r="F17" s="16"/>
+      <c r="F17" s="15"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="11">
         <v>-0.23719660000000001</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="11">
         <v>9.3477199999999996E-2</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="9">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="F18" s="16"/>
+      <c r="F18" s="15"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="11">
         <v>1.6128E-3</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="11">
         <v>0.1071569</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="9">
         <v>0.98799999999999999</v>
       </c>
-      <c r="F19" s="16"/>
+      <c r="F19" s="15"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="11">
         <v>-8.8836700000000005E-2</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="11">
         <v>9.5828999999999998E-2</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="9">
         <v>0.35399999999999998</v>
       </c>
-      <c r="F20" s="16"/>
+      <c r="F20" s="15"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="11">
         <v>-8.4288600000000005E-2</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="11">
         <v>0.1237255</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="9">
         <v>0.496</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="13">
         <v>-1.9734039999999999</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13">
         <v>0.11475200000000001</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -46624,25 +46448,25 @@
         <v>105239</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="11">
         <v>8.14E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="11" t="s">
+    <row r="25" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="10">
         <v>0.33410000000000001</v>
       </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
     </row>
-    <row r="26" spans="1:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -46651,334 +46475,334 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1700754-15D1-4FAA-B4AF-AB487BD81AF9}">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.7265625" customWidth="1"/>
+    <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="9" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="11">
         <v>5.9753109999999996</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="11">
         <v>1.446493</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <v>0</v>
       </c>
-      <c r="F3" s="16"/>
-      <c r="H3" s="16"/>
+      <c r="F3" s="15"/>
+      <c r="H3" s="15"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="10"/>
-      <c r="F4" s="16"/>
-      <c r="H4" s="16"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="9"/>
+      <c r="F4" s="15"/>
+      <c r="H4" s="15"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <v>-0.24413109999999999</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="11">
         <v>0.16255240000000001</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <v>0.13300000000000001</v>
       </c>
-      <c r="F5" s="16"/>
-      <c r="H5" s="16"/>
+      <c r="F5" s="15"/>
+      <c r="H5" s="15"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <v>-0.58418099999999995</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="11">
         <v>0.14954229999999999</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <v>0</v>
       </c>
-      <c r="F6" s="16"/>
-      <c r="H6" s="16"/>
+      <c r="F6" s="15"/>
+      <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="11">
         <v>-0.73888339999999997</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="11">
         <v>0.14546190000000001</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <v>0</v>
       </c>
-      <c r="F7" s="16"/>
-      <c r="H7" s="16"/>
+      <c r="F7" s="15"/>
+      <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="11">
         <v>-0.68960630000000001</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="11">
         <v>0.15277589999999999</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <v>0</v>
       </c>
-      <c r="F8" s="16"/>
-      <c r="H8" s="16"/>
+      <c r="F8" s="15"/>
+      <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="11">
         <v>0.99962569999999995</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="11">
         <v>6.0135099999999997E-2</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <v>0</v>
       </c>
-      <c r="F9" s="16"/>
-      <c r="H9" s="16"/>
+      <c r="F9" s="15"/>
+      <c r="H9" s="15"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="10"/>
-      <c r="F10" s="16"/>
-      <c r="H10" s="16"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="9"/>
+      <c r="F10" s="15"/>
+      <c r="H10" s="15"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>1.25781E-2</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="11">
         <v>0.13117690000000001</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <v>0.92400000000000004</v>
       </c>
-      <c r="F11" s="16"/>
-      <c r="H11" s="16"/>
+      <c r="F11" s="15"/>
+      <c r="H11" s="15"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="11">
         <v>-0.25731369999999998</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="11">
         <v>0.1018121</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="F12" s="16"/>
-      <c r="H12" s="16"/>
+      <c r="F12" s="15"/>
+      <c r="H12" s="15"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="11">
         <v>-5.4468900000000001E-2</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="11">
         <v>0.148701</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <v>0.71399999999999997</v>
       </c>
-      <c r="F13" s="16"/>
-      <c r="H13" s="16"/>
+      <c r="F13" s="15"/>
+      <c r="H13" s="15"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="11">
         <v>-5.1002499999999999E-2</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="11">
         <v>0.1276919</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <v>0.69</v>
       </c>
-      <c r="F14" s="16"/>
-      <c r="H14" s="16"/>
+      <c r="F14" s="15"/>
+      <c r="H14" s="15"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="11">
         <v>-0.32287589999999999</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="11">
         <v>0.12618650000000001</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="9">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="F15" s="16"/>
-      <c r="H15" s="16"/>
+      <c r="F15" s="15"/>
+      <c r="H15" s="15"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="11">
         <v>-0.1222989</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="11">
         <v>0.11936239999999999</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="9">
         <v>0.30599999999999999</v>
       </c>
-      <c r="F16" s="16"/>
-      <c r="H16" s="16"/>
+      <c r="F16" s="15"/>
+      <c r="H16" s="15"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="11">
         <v>-0.1957014</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="11">
         <v>9.4777700000000006E-2</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <v>3.9E-2</v>
       </c>
-      <c r="F17" s="16"/>
-      <c r="H17" s="16"/>
+      <c r="F17" s="15"/>
+      <c r="H17" s="15"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="11">
         <v>-0.29324670000000003</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="11">
         <v>0.1154872</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="9">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="F18" s="16"/>
-      <c r="H18" s="16"/>
+      <c r="F18" s="15"/>
+      <c r="H18" s="15"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="11">
         <v>-9.8002500000000006E-2</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="11">
         <v>0.15076310000000001</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="9">
         <v>0.51600000000000001</v>
       </c>
-      <c r="F19" s="16"/>
-      <c r="H19" s="16"/>
+      <c r="F19" s="15"/>
+      <c r="H19" s="15"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="11">
         <v>-0.2358585</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="11">
         <v>0.1205817</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="9">
         <v>0.05</v>
       </c>
-      <c r="F20" s="16"/>
-      <c r="H20" s="16"/>
+      <c r="F20" s="15"/>
+      <c r="H20" s="15"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="11">
         <v>-2.1484E-2</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="11">
         <v>0.1725748</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="9">
         <v>0.90100000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="13">
         <v>-1.679454</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13">
         <v>0.15840760000000001</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -46986,25 +46810,25 @@
         <v>51984</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="11">
         <v>2.7699999999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="11" t="s">
+    <row r="25" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="10">
         <v>0.14860000000000001</v>
       </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
     </row>
-    <row r="26" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -47013,334 +46837,334 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC354731-ABAD-4A25-A806-32C67693DC3F}">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" customWidth="1"/>
+    <col min="1" max="1" width="25.7265625" customWidth="1"/>
+    <col min="2" max="2" width="10.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="9" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="11">
         <v>3.7763939999999998</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="11">
         <v>0.44900820000000002</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <v>0</v>
       </c>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="10"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="9"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <v>-3.5162699999999998E-2</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="11">
         <v>7.6697299999999996E-2</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <v>0.64700000000000002</v>
       </c>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <v>-0.2660516</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="11">
         <v>7.3663800000000001E-2</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <v>0</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="11">
         <v>-0.38286730000000002</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="11">
         <v>7.5167200000000003E-2</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <v>0</v>
       </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="11">
         <v>-0.341922</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="11">
         <v>8.3535499999999999E-2</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <v>0</v>
       </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="11">
         <v>1.1644049999999999</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="11">
         <v>3.3356499999999997E-2</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <v>0</v>
       </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="10"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="9"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>-5.3546099999999999E-2</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="11">
         <v>8.3766499999999994E-2</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <v>0.52300000000000002</v>
       </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="11">
         <v>-0.11467570000000001</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="11">
         <v>6.8276100000000006E-2</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="11">
         <v>-0.1211295</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="11">
         <v>7.6071399999999997E-2</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <v>0.111</v>
       </c>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="11">
         <v>-0.2774856</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="11">
         <v>8.2540500000000003E-2</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <v>1E-3</v>
       </c>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="11">
         <v>-7.3163800000000001E-2</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="11">
         <v>6.8430599999999994E-2</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="9">
         <v>0.28499999999999998</v>
       </c>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="11">
         <v>-0.35890030000000001</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="11">
         <v>7.4285900000000002E-2</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="9">
         <v>0</v>
       </c>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="11">
         <v>-0.28771619999999998</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="11">
         <v>7.1416800000000003E-2</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <v>0</v>
       </c>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="11">
         <v>-0.39531179999999999</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="11">
         <v>7.5965199999999997E-2</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="9">
         <v>0</v>
       </c>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="11">
         <v>-0.18245339999999999</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="11">
         <v>9.4520800000000002E-2</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="9">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="11">
         <v>-5.7001599999999999E-2</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="11">
         <v>7.7373399999999995E-2</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="9">
         <v>0.46100000000000002</v>
       </c>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="11">
         <v>-1.4298E-3</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="11">
         <v>9.6062400000000006E-2</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="9">
         <v>0.98799999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="13">
         <v>-1.8207439999999999</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13">
         <v>8.9084999999999998E-2</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -47348,25 +47172,25 @@
         <v>124166</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="11">
         <v>5.8099999999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="11" t="s">
+    <row r="25" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="10">
         <v>0.1991</v>
       </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
     </row>
-    <row r="26" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/input/reg_unemployment.xlsx
+++ b/input/reg_unemployment.xlsx
@@ -1,31 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFiles\99 DEV ENV\temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{788E7650-F9FB-423B-B256-A540CD4A015F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE24C2C-50F3-6148-BF86-0684F454CF21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="3" activeTab="12" xr2:uid="{CC9AB010-6F1C-42A2-A1E7-CC06071EB15C}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17820" firstSheet="3" activeTab="12" xr2:uid="{CC9AB010-6F1C-42A2-A1E7-CC06071EB15C}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
-    <sheet name="UK_U1a" sheetId="8" r:id="rId2"/>
-    <sheet name="UK_U1b" sheetId="10" r:id="rId3"/>
-    <sheet name="UK_U1c" sheetId="14" r:id="rId4"/>
-    <sheet name="UK_U1d" sheetId="15" r:id="rId5"/>
+    <sheet name="U1a" sheetId="8" r:id="rId2"/>
+    <sheet name="U1b" sheetId="10" r:id="rId3"/>
+    <sheet name="U1c" sheetId="14" r:id="rId4"/>
+    <sheet name="U1d" sheetId="15" r:id="rId5"/>
     <sheet name="Process U1a" sheetId="9" r:id="rId6"/>
     <sheet name="Process U1b" sheetId="11" r:id="rId7"/>
     <sheet name="Process U1c" sheetId="12" r:id="rId8"/>
     <sheet name="Process U1d" sheetId="13" r:id="rId9"/>
-    <sheet name="UK_RatesMaleGraduates" sheetId="3" r:id="rId10"/>
-    <sheet name="UK_RatesMaleNonGraduates" sheetId="4" r:id="rId11"/>
-    <sheet name="UK_RatesFemaleGraduates" sheetId="6" r:id="rId12"/>
-    <sheet name="UK_RatesFemaleNonGraduates" sheetId="7" r:id="rId13"/>
+    <sheet name="RatesMaleGraduates" sheetId="3" r:id="rId10"/>
+    <sheet name="RatesMaleNonGraduates" sheetId="4" r:id="rId11"/>
+    <sheet name="RatesFemaleGraduates" sheetId="6" r:id="rId12"/>
+    <sheet name="RatesFemaleNonGraduates" sheetId="7" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -732,12 +732,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5DD3FED-033E-405B-A2A7-67A35968B641}">
   <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -745,7 +745,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>70</v>
       </c>
@@ -753,7 +753,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -761,7 +761,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -769,11 +769,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
@@ -781,7 +781,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -792,7 +792,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -800,7 +800,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -808,7 +808,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -816,7 +816,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -825,7 +825,7 @@
         <v>Probit regression estimates of unemployment for male graduates (aged 18 to 64)</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>67</v>
       </c>
@@ -834,7 +834,7 @@
         <v>Probit regression estimates of unemployment for male non-graduates (aged 18 to 64)</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -843,7 +843,7 @@
         <v>Probit regression estimates of unemployment for female graduates (aged 18 to 64)</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>69</v>
       </c>
@@ -860,13 +860,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28EC0B5F-04C9-4F5F-A901-B8AAE6DEDE0A}">
   <dimension ref="A1:AX66"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="4" width="8.81640625" style="4"/>
-    <col min="5" max="16384" width="8.81640625" style="5"/>
+    <col min="1" max="4" width="8.83203125" style="4"/>
+    <col min="5" max="16384" width="8.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="2" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>16</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>0.32057885000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>17</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>0.24913356000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>18</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>0.19593476999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>19</v>
       </c>
@@ -1626,7 +1626,7 @@
         <v>0.17182712999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>20</v>
       </c>
@@ -1778,7 +1778,7 @@
         <v>0.15967402</v>
       </c>
     </row>
-    <row r="7" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>21</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>0.13140270999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>22</v>
       </c>
@@ -2082,7 +2082,7 @@
         <v>0.1082795</v>
       </c>
     </row>
-    <row r="9" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>23</v>
       </c>
@@ -2234,7 +2234,7 @@
         <v>8.8274959999999986E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>24</v>
       </c>
@@ -2386,7 +2386,7 @@
         <v>6.5812979999999993E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>25</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>5.5256269999999996E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>26</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>3.6772130000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>27</v>
       </c>
@@ -2842,7 +2842,7 @@
         <v>3.6527290000000004E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>28</v>
       </c>
@@ -2994,7 +2994,7 @@
         <v>2.6608559999999996E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>29</v>
       </c>
@@ -3146,7 +3146,7 @@
         <v>2.5161919999999997E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>30</v>
       </c>
@@ -3298,7 +3298,7 @@
         <v>2.468074E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>31</v>
       </c>
@@ -3450,7 +3450,7 @@
         <v>1.5728199999999998E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>32</v>
       </c>
@@ -3602,7 +3602,7 @@
         <v>2.0821219999999998E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>33</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>1.7944900000000003E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>34</v>
       </c>
@@ -3906,7 +3906,7 @@
         <v>1.3482890000000001E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>35</v>
       </c>
@@ -4058,7 +4058,7 @@
         <v>1.324671E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>36</v>
       </c>
@@ -4210,7 +4210,7 @@
         <v>1.6916359999999998E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>37</v>
       </c>
@@ -4362,7 +4362,7 @@
         <v>1.8430700000000001E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>38</v>
       </c>
@@ -4514,7 +4514,7 @@
         <v>1.3897240000000002E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>39</v>
       </c>
@@ -4666,7 +4666,7 @@
         <v>1.690589E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="6">
         <v>40</v>
       </c>
@@ -4818,7 +4818,7 @@
         <v>1.564217E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="6">
         <v>41</v>
       </c>
@@ -4970,7 +4970,7 @@
         <v>1.845892E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>42</v>
       </c>
@@ -5122,7 +5122,7 @@
         <v>2.5302109999999999E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
         <v>43</v>
       </c>
@@ -5274,7 +5274,7 @@
         <v>2.0708589999999999E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A30" s="6">
         <v>44</v>
       </c>
@@ -5426,7 +5426,7 @@
         <v>2.0847170000000005E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A31" s="6">
         <v>45</v>
       </c>
@@ -5578,7 +5578,7 @@
         <v>1.7571759999999999E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A32" s="6">
         <v>46</v>
       </c>
@@ -5730,7 +5730,7 @@
         <v>1.7073720000000001E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A33" s="6">
         <v>47</v>
       </c>
@@ -5882,7 +5882,7 @@
         <v>2.44919E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A34" s="6">
         <v>48</v>
       </c>
@@ -6034,7 +6034,7 @@
         <v>2.5936340000000002E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
         <v>49</v>
       </c>
@@ -6186,7 +6186,7 @@
         <v>2.3026539999999998E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="6">
         <v>50</v>
       </c>
@@ -6338,7 +6338,7 @@
         <v>2.5105870000000002E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <v>51</v>
       </c>
@@ -6490,7 +6490,7 @@
         <v>1.7104889999999998E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <v>52</v>
       </c>
@@ -6642,7 +6642,7 @@
         <v>2.5441709999999999E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <v>53</v>
       </c>
@@ -6794,7 +6794,7 @@
         <v>2.0940939999999998E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <v>54</v>
       </c>
@@ -6946,7 +6946,7 @@
         <v>3.389872E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <v>55</v>
       </c>
@@ -7098,7 +7098,7 @@
         <v>3.100603E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="6">
         <v>56</v>
       </c>
@@ -7250,7 +7250,7 @@
         <v>2.6832839999999997E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="6">
         <v>57</v>
       </c>
@@ -7402,7 +7402,7 @@
         <v>3.1260670000000004E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="6">
         <v>58</v>
       </c>
@@ -7554,7 +7554,7 @@
         <v>2.4161920000000003E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="6">
         <v>59</v>
       </c>
@@ -7706,7 +7706,7 @@
         <v>2.5432729999999997E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="6">
         <v>60</v>
       </c>
@@ -7858,7 +7858,7 @@
         <v>3.0238820000000007E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A47" s="6">
         <v>61</v>
       </c>
@@ -8010,7 +8010,7 @@
         <v>2.2392189999999999E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="6">
         <v>62</v>
       </c>
@@ -8162,7 +8162,7 @@
         <v>2.741072E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A49" s="6">
         <v>63</v>
       </c>
@@ -8314,7 +8314,7 @@
         <v>2.356635E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A50" s="6">
         <v>64</v>
       </c>
@@ -8466,7 +8466,7 @@
         <v>3.1952790000000002E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A51" s="6">
         <v>65</v>
       </c>
@@ -8618,7 +8618,7 @@
         <v>3.9330740624999992E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A52" s="6">
         <v>66</v>
       </c>
@@ -8770,7 +8770,7 @@
         <v>4.6708691249999996E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A53" s="6">
         <v>67</v>
       </c>
@@ -8922,7 +8922,7 @@
         <v>5.4086641875000008E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A54" s="6">
         <v>68</v>
       </c>
@@ -9074,7 +9074,7 @@
         <v>6.1464592499999991E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A55" s="6">
         <v>69</v>
       </c>
@@ -9226,7 +9226,7 @@
         <v>6.8842543125000003E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A56" s="6">
         <v>70</v>
       </c>
@@ -9378,7 +9378,7 @@
         <v>7.6220493750000007E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A57" s="6">
         <v>71</v>
       </c>
@@ -9530,7 +9530,7 @@
         <v>8.3598444375000011E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A58" s="6">
         <v>72</v>
       </c>
@@ -9682,7 +9682,7 @@
         <v>9.0976395000000015E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A59" s="6">
         <v>73</v>
       </c>
@@ -9834,7 +9834,7 @@
         <v>9.8354345625000006E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A60" s="6">
         <v>74</v>
       </c>
@@ -9986,7 +9986,7 @@
         <v>0.10573229625000002</v>
       </c>
     </row>
-    <row r="61" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A61" s="6">
         <v>75</v>
       </c>
@@ -10138,7 +10138,7 @@
         <v>0.11311024687500001</v>
       </c>
     </row>
-    <row r="62" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A62" s="6">
         <v>76</v>
       </c>
@@ -10290,7 +10290,7 @@
         <v>0.12048819750000002</v>
       </c>
     </row>
-    <row r="63" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A63" s="6">
         <v>77</v>
       </c>
@@ -10442,7 +10442,7 @@
         <v>0.12786614812500002</v>
       </c>
     </row>
-    <row r="64" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A64" s="6">
         <v>78</v>
       </c>
@@ -10594,7 +10594,7 @@
         <v>0.13524409875000004</v>
       </c>
     </row>
-    <row r="65" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A65" s="6">
         <v>79</v>
       </c>
@@ -10746,7 +10746,7 @@
         <v>0.14262204937500006</v>
       </c>
     </row>
-    <row r="66" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A66" s="6">
         <v>80</v>
       </c>
@@ -10906,13 +10906,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9172C708-9303-4B74-B36A-400E8C4455B4}">
   <dimension ref="A1:AX66"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="2" width="8.81640625" style="4"/>
-    <col min="3" max="16384" width="8.81640625" style="5"/>
+    <col min="1" max="2" width="8.83203125" style="4"/>
+    <col min="3" max="16384" width="8.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
@@ -11064,7 +11064,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="2" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>16</v>
       </c>
@@ -11216,7 +11216,7 @@
         <v>0.32057885000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>17</v>
       </c>
@@ -11368,7 +11368,7 @@
         <v>0.24913356000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>18</v>
       </c>
@@ -11520,7 +11520,7 @@
         <v>0.19593476999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>19</v>
       </c>
@@ -11672,7 +11672,7 @@
         <v>0.17182712999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>20</v>
       </c>
@@ -11824,7 +11824,7 @@
         <v>0.15967402</v>
       </c>
     </row>
-    <row r="7" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>21</v>
       </c>
@@ -11976,7 +11976,7 @@
         <v>0.13140270999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>22</v>
       </c>
@@ -12128,7 +12128,7 @@
         <v>0.1082795</v>
       </c>
     </row>
-    <row r="9" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>23</v>
       </c>
@@ -12280,7 +12280,7 @@
         <v>9.5490260000000007E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>24</v>
       </c>
@@ -12432,7 +12432,7 @@
         <v>8.6285799999999996E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>25</v>
       </c>
@@ -12584,7 +12584,7 @@
         <v>7.5845690000000007E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>26</v>
       </c>
@@ -12736,7 +12736,7 @@
         <v>5.0565230000000003E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>27</v>
       </c>
@@ -12888,7 +12888,7 @@
         <v>5.3880789999999998E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>28</v>
       </c>
@@ -13040,7 +13040,7 @@
         <v>4.4968840000000003E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>29</v>
       </c>
@@ -13192,7 +13192,7 @@
         <v>3.7355399999999997E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>30</v>
       </c>
@@ -13344,7 +13344,7 @@
         <v>3.4893949999999993E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>31</v>
       </c>
@@ -13496,7 +13496,7 @@
         <v>3.1849840000000004E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>32</v>
       </c>
@@ -13648,7 +13648,7 @@
         <v>3.3739389999999994E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>33</v>
       </c>
@@ -13800,7 +13800,7 @@
         <v>2.798235E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>34</v>
       </c>
@@ -13952,7 +13952,7 @@
         <v>2.8765629999999997E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>35</v>
       </c>
@@ -14104,7 +14104,7 @@
         <v>2.9261849999999999E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>36</v>
       </c>
@@ -14256,7 +14256,7 @@
         <v>2.8418540000000003E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>37</v>
       </c>
@@ -14408,7 +14408,7 @@
         <v>2.8308900000000005E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>38</v>
       </c>
@@ -14560,7 +14560,7 @@
         <v>2.5911989999999996E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>39</v>
       </c>
@@ -14712,7 +14712,7 @@
         <v>3.2470720000000002E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="6">
         <v>40</v>
       </c>
@@ -14864,7 +14864,7 @@
         <v>2.8177269999999997E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="6">
         <v>41</v>
       </c>
@@ -15016,7 +15016,7 @@
         <v>2.7782039999999997E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>42</v>
       </c>
@@ -15168,7 +15168,7 @@
         <v>2.7246860000000001E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
         <v>43</v>
       </c>
@@ -15320,7 +15320,7 @@
         <v>2.7496179999999999E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A30" s="6">
         <v>44</v>
       </c>
@@ -15472,7 +15472,7 @@
         <v>2.6858360000000005E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A31" s="6">
         <v>45</v>
       </c>
@@ -15624,7 +15624,7 @@
         <v>3.0459229999999997E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A32" s="6">
         <v>46</v>
       </c>
@@ -15776,7 +15776,7 @@
         <v>2.7958719999999999E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A33" s="6">
         <v>47</v>
       </c>
@@ -15928,7 +15928,7 @@
         <v>3.191956E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A34" s="6">
         <v>48</v>
       </c>
@@ -16080,7 +16080,7 @@
         <v>2.8831089999999997E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
         <v>49</v>
       </c>
@@ -16232,7 +16232,7 @@
         <v>3.1578700000000001E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="6">
         <v>50</v>
       </c>
@@ -16384,7 +16384,7 @@
         <v>2.8726309999999998E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <v>51</v>
       </c>
@@ -16536,7 +16536,7 @@
         <v>2.8136230000000002E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <v>52</v>
       </c>
@@ -16688,7 +16688,7 @@
         <v>3.225426E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <v>53</v>
       </c>
@@ -16840,7 +16840,7 @@
         <v>2.4534540000000001E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <v>54</v>
       </c>
@@ -16992,7 +16992,7 @@
         <v>3.5306339999999999E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <v>55</v>
       </c>
@@ -17144,7 +17144,7 @@
         <v>3.5951499999999997E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="6">
         <v>56</v>
       </c>
@@ -17296,7 +17296,7 @@
         <v>3.3881160000000007E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="6">
         <v>57</v>
       </c>
@@ -17448,7 +17448,7 @@
         <v>3.6523029999999998E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="6">
         <v>58</v>
       </c>
@@ -17600,7 +17600,7 @@
         <v>3.5319530000000002E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="6">
         <v>59</v>
       </c>
@@ -17752,7 +17752,7 @@
         <v>3.3760220000000001E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="6">
         <v>60</v>
       </c>
@@ -17904,7 +17904,7 @@
         <v>3.87558E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A47" s="6">
         <v>61</v>
       </c>
@@ -18056,7 +18056,7 @@
         <v>4.1845160000000006E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="6">
         <v>62</v>
       </c>
@@ -18208,7 +18208,7 @@
         <v>3.9918290000000002E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A49" s="6">
         <v>63</v>
       </c>
@@ -18360,7 +18360,7 @@
         <v>3.7733380000000004E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A50" s="6">
         <v>64</v>
       </c>
@@ -18512,7 +18512,7 @@
         <v>4.260179E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A51" s="6">
         <v>65</v>
       </c>
@@ -18664,7 +18664,7 @@
         <v>4.1939197999999997E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A52" s="6">
         <v>66</v>
       </c>
@@ -18816,7 +18816,7 @@
         <v>4.9143251466666656E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A53" s="6">
         <v>67</v>
       </c>
@@ -18968,7 +18968,7 @@
         <v>5.6347304933333328E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A54" s="6">
         <v>68</v>
       </c>
@@ -19120,7 +19120,7 @@
         <v>6.355135839999998E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A55" s="6">
         <v>69</v>
       </c>
@@ -19272,7 +19272,7 @@
         <v>7.0755411866666659E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A56" s="6">
         <v>70</v>
       </c>
@@ -19424,7 +19424,7 @@
         <v>7.7959465333333339E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A57" s="6">
         <v>71</v>
       </c>
@@ -19576,7 +19576,7 @@
         <v>8.5163518799999977E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A58" s="6">
         <v>72</v>
       </c>
@@ -19728,7 +19728,7 @@
         <v>9.2367572266666642E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A59" s="6">
         <v>73</v>
       </c>
@@ -19880,7 +19880,7 @@
         <v>9.9571625733333335E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A60" s="6">
         <v>74</v>
       </c>
@@ -20032,7 +20032,7 @@
         <v>0.1067756792</v>
       </c>
     </row>
-    <row r="61" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A61" s="6">
         <v>75</v>
       </c>
@@ -20184,7 +20184,7 @@
         <v>0.11397973266666664</v>
       </c>
     </row>
-    <row r="62" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A62" s="6">
         <v>76</v>
       </c>
@@ -20336,7 +20336,7 @@
         <v>0.12118378613333332</v>
       </c>
     </row>
-    <row r="63" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A63" s="6">
         <v>77</v>
       </c>
@@ -20488,7 +20488,7 @@
         <v>0.12838783959999994</v>
       </c>
     </row>
-    <row r="64" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A64" s="6">
         <v>78</v>
       </c>
@@ -20640,7 +20640,7 @@
         <v>0.13559189306666666</v>
       </c>
     </row>
-    <row r="65" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A65" s="6">
         <v>79</v>
       </c>
@@ -20792,7 +20792,7 @@
         <v>0.14279594653333333</v>
       </c>
     </row>
-    <row r="66" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A66" s="6">
         <v>80</v>
       </c>
@@ -20952,13 +20952,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36656541-FCAB-471F-B3CC-C2331CBC317D}">
   <dimension ref="A1:AX66"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="4" width="8.81640625" style="4"/>
-    <col min="5" max="16384" width="8.81640625" style="5"/>
+    <col min="1" max="4" width="8.83203125" style="4"/>
+    <col min="5" max="16384" width="8.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
@@ -21110,7 +21110,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="2" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>16</v>
       </c>
@@ -21262,7 +21262,7 @@
         <v>0.26019811999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>17</v>
       </c>
@@ -21414,7 +21414,7 @@
         <v>0.18180854000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>18</v>
       </c>
@@ -21566,7 +21566,7 @@
         <v>0.14871978999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>19</v>
       </c>
@@ -21718,7 +21718,7 @@
         <v>0.14520216999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>20</v>
       </c>
@@ -21870,7 +21870,7 @@
         <v>9.8097610000000016E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>21</v>
       </c>
@@ -22022,7 +22022,7 @@
         <v>8.9078409999999997E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>22</v>
       </c>
@@ -22174,7 +22174,7 @@
         <v>8.8558600000000001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>23</v>
       </c>
@@ -22326,7 +22326,7 @@
         <v>5.0640470000000007E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>24</v>
       </c>
@@ -22478,7 +22478,7 @@
         <v>4.37875E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>25</v>
       </c>
@@ -22630,7 +22630,7 @@
         <v>3.5014460000000004E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>26</v>
       </c>
@@ -22782,7 +22782,7 @@
         <v>2.1639590000000004E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>27</v>
       </c>
@@ -22934,7 +22934,7 @@
         <v>2.6975739999999998E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>28</v>
       </c>
@@ -23086,7 +23086,7 @@
         <v>3.2589880000000002E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>29</v>
       </c>
@@ -23238,7 +23238,7 @@
         <v>1.9616940000000003E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>30</v>
       </c>
@@ -23390,7 +23390,7 @@
         <v>2.8011589999999996E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>31</v>
       </c>
@@ -23542,7 +23542,7 @@
         <v>2.2562310000000002E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>32</v>
       </c>
@@ -23694,7 +23694,7 @@
         <v>2.8440979999999998E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>33</v>
       </c>
@@ -23846,7 +23846,7 @@
         <v>2.2318650000000002E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>34</v>
       </c>
@@ -23998,7 +23998,7 @@
         <v>2.2305889999999998E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>35</v>
       </c>
@@ -24150,7 +24150,7 @@
         <v>2.1616710000000001E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>36</v>
       </c>
@@ -24302,7 +24302,7 @@
         <v>1.7932989999999999E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>37</v>
       </c>
@@ -24454,7 +24454,7 @@
         <v>1.9648470000000001E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>38</v>
       </c>
@@ -24606,7 +24606,7 @@
         <v>2.0679350000000006E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>39</v>
       </c>
@@ -24758,7 +24758,7 @@
         <v>2.6637729999999998E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="6">
         <v>40</v>
       </c>
@@ -24910,7 +24910,7 @@
         <v>1.9886649999999999E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="6">
         <v>41</v>
       </c>
@@ -25062,7 +25062,7 @@
         <v>1.955728E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>42</v>
       </c>
@@ -25214,7 +25214,7 @@
         <v>2.2265529999999999E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
         <v>43</v>
       </c>
@@ -25366,7 +25366,7 @@
         <v>2.2124769999999998E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A30" s="6">
         <v>44</v>
       </c>
@@ -25518,7 +25518,7 @@
         <v>2.075113E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A31" s="6">
         <v>45</v>
       </c>
@@ -25670,7 +25670,7 @@
         <v>1.851042E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A32" s="6">
         <v>46</v>
       </c>
@@ -25822,7 +25822,7 @@
         <v>2.3261609999999999E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A33" s="6">
         <v>47</v>
       </c>
@@ -25974,7 +25974,7 @@
         <v>3.0736720000000006E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A34" s="6">
         <v>48</v>
       </c>
@@ -26126,7 +26126,7 @@
         <v>1.7331159999999998E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
         <v>49</v>
       </c>
@@ -26278,7 +26278,7 @@
         <v>2.0583360000000002E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="6">
         <v>50</v>
       </c>
@@ -26430,7 +26430,7 @@
         <v>1.68921E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <v>51</v>
       </c>
@@ -26582,7 +26582,7 @@
         <v>1.2943199999999998E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <v>52</v>
       </c>
@@ -26734,7 +26734,7 @@
         <v>1.6397169999999999E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <v>53</v>
       </c>
@@ -26886,7 +26886,7 @@
         <v>2.2326510000000001E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <v>54</v>
       </c>
@@ -27038,7 +27038,7 @@
         <v>1.9069510000000001E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <v>55</v>
       </c>
@@ -27190,7 +27190,7 @@
         <v>2.4882430000000001E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="6">
         <v>56</v>
       </c>
@@ -27342,7 +27342,7 @@
         <v>2.275458E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="6">
         <v>57</v>
       </c>
@@ -27494,7 +27494,7 @@
         <v>1.7978999999999998E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="6">
         <v>58</v>
       </c>
@@ -27646,7 +27646,7 @@
         <v>2.0993350000000001E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="6">
         <v>59</v>
       </c>
@@ -27798,7 +27798,7 @@
         <v>1.9619069999999995E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="6">
         <v>60</v>
       </c>
@@ -27950,7 +27950,7 @@
         <v>2.1355597999999996E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A47" s="6">
         <v>61</v>
       </c>
@@ -28102,7 +28102,7 @@
         <v>2.77878181E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="6">
         <v>62</v>
       </c>
@@ -28254,7 +28254,7 @@
         <v>3.422003819999999E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A49" s="6">
         <v>63</v>
       </c>
@@ -28406,7 +28406,7 @@
         <v>4.0652258300000001E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A50" s="6">
         <v>64</v>
       </c>
@@ -28558,7 +28558,7 @@
         <v>4.7084478400000004E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A51" s="6">
         <v>65</v>
       </c>
@@ -28710,7 +28710,7 @@
         <v>5.3516698500000001E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A52" s="6">
         <v>66</v>
       </c>
@@ -28862,7 +28862,7 @@
         <v>5.9948918599999991E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A53" s="6">
         <v>67</v>
       </c>
@@ -29014,7 +29014,7 @@
         <v>6.6381138699999995E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A54" s="6">
         <v>68</v>
       </c>
@@ -29166,7 +29166,7 @@
         <v>7.2813358800000005E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A55" s="6">
         <v>69</v>
       </c>
@@ -29318,7 +29318,7 @@
         <v>7.9245578900000002E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A56" s="6">
         <v>70</v>
       </c>
@@ -29470,7 +29470,7 @@
         <v>8.5677798999999999E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A57" s="6">
         <v>71</v>
       </c>
@@ -29622,7 +29622,7 @@
         <v>9.211001910000001E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A58" s="6">
         <v>72</v>
       </c>
@@ -29774,7 +29774,7 @@
         <v>9.8542239199999992E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A59" s="6">
         <v>73</v>
       </c>
@@ -29926,7 +29926,7 @@
         <v>0.1049744593</v>
       </c>
     </row>
-    <row r="60" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A60" s="6">
         <v>74</v>
       </c>
@@ -30078,7 +30078,7 @@
         <v>0.11140667940000001</v>
       </c>
     </row>
-    <row r="61" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A61" s="6">
         <v>75</v>
       </c>
@@ -30230,7 +30230,7 @@
         <v>0.1178388995</v>
       </c>
     </row>
-    <row r="62" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A62" s="6">
         <v>76</v>
       </c>
@@ -30382,7 +30382,7 @@
         <v>0.12427111960000001</v>
       </c>
     </row>
-    <row r="63" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A63" s="6">
         <v>77</v>
       </c>
@@ -30534,7 +30534,7 @@
         <v>0.13070333969999998</v>
       </c>
     </row>
-    <row r="64" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A64" s="6">
         <v>78</v>
       </c>
@@ -30686,7 +30686,7 @@
         <v>0.1371355598</v>
       </c>
     </row>
-    <row r="65" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A65" s="6">
         <v>79</v>
       </c>
@@ -30838,7 +30838,7 @@
         <v>0.1435677799</v>
       </c>
     </row>
-    <row r="66" spans="1:50" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:50" ht="15" x14ac:dyDescent="0.2">
       <c r="A66" s="6">
         <v>80</v>
       </c>
@@ -30998,9 +30998,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E2C5941-0F60-4C3F-9BA6-C77841CC7AAE}">
   <dimension ref="A1:AX66"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
@@ -31152,7 +31152,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>16</v>
       </c>
@@ -31304,7 +31304,7 @@
         <v>0.26019811999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>17</v>
       </c>
@@ -31456,7 +31456,7 @@
         <v>0.18180854000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>18</v>
       </c>
@@ -31608,7 +31608,7 @@
         <v>0.14871978999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>19</v>
       </c>
@@ -31760,7 +31760,7 @@
         <v>0.14520216999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>20</v>
       </c>
@@ -31912,7 +31912,7 @@
         <v>9.8097610000000016E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>21</v>
       </c>
@@ -32064,7 +32064,7 @@
         <v>8.9078409999999997E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>22</v>
       </c>
@@ -32216,7 +32216,7 @@
         <v>8.8558600000000001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>23</v>
       </c>
@@ -32368,7 +32368,7 @@
         <v>6.745232000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>24</v>
       </c>
@@ -32520,7 +32520,7 @@
         <v>5.5023500000000003E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>25</v>
       </c>
@@ -32672,7 +32672,7 @@
         <v>5.0879679999999997E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>26</v>
       </c>
@@ -32824,7 +32824,7 @@
         <v>4.0940579999999997E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>27</v>
       </c>
@@ -32976,7 +32976,7 @@
         <v>4.0392439999999995E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>28</v>
       </c>
@@ -33128,7 +33128,7 @@
         <v>4.8918830000000003E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>29</v>
       </c>
@@ -33280,7 +33280,7 @@
         <v>3.957198E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>30</v>
       </c>
@@ -33432,7 +33432,7 @@
         <v>4.2480329999999997E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>31</v>
       </c>
@@ -33584,7 +33584,7 @@
         <v>3.3808650000000003E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>32</v>
       </c>
@@ -33736,7 +33736,7 @@
         <v>4.0517319999999996E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>33</v>
       </c>
@@ -33888,7 +33888,7 @@
         <v>3.591602E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>34</v>
       </c>
@@ -34040,7 +34040,7 @@
         <v>3.6668350000000002E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>35</v>
       </c>
@@ -34192,7 +34192,7 @@
         <v>3.8220319999999995E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>36</v>
       </c>
@@ -34344,7 +34344,7 @@
         <v>2.8513329999999996E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>37</v>
       </c>
@@ -34496,7 +34496,7 @@
         <v>3.1724290000000002E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>38</v>
       </c>
@@ -34648,7 +34648,7 @@
         <v>2.9454850000000005E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>39</v>
       </c>
@@ -34800,7 +34800,7 @@
         <v>3.7669190000000005E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A26" s="6">
         <v>40</v>
       </c>
@@ -34952,7 +34952,7 @@
         <v>3.0450950000000004E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A27" s="6">
         <v>41</v>
       </c>
@@ -35104,7 +35104,7 @@
         <v>3.1953229999999999E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>42</v>
       </c>
@@ -35256,7 +35256,7 @@
         <v>3.1920499999999997E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
         <v>43</v>
       </c>
@@ -35408,7 +35408,7 @@
         <v>3.1741510000000001E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A30" s="6">
         <v>44</v>
       </c>
@@ -35560,7 +35560,7 @@
         <v>3.3504269999999996E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A31" s="6">
         <v>45</v>
       </c>
@@ -35712,7 +35712,7 @@
         <v>3.0541649999999997E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A32" s="6">
         <v>46</v>
       </c>
@@ -35864,7 +35864,7 @@
         <v>3.1189939999999999E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A33" s="6">
         <v>47</v>
       </c>
@@ -36016,7 +36016,7 @@
         <v>3.5657000000000001E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A34" s="6">
         <v>48</v>
       </c>
@@ -36168,7 +36168,7 @@
         <v>2.8557769999999993E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
         <v>49</v>
       </c>
@@ -36320,7 +36320,7 @@
         <v>2.6860820000000001E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A36" s="6">
         <v>50</v>
       </c>
@@ -36472,7 +36472,7 @@
         <v>2.3105970000000003E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <v>51</v>
       </c>
@@ -36624,7 +36624,7 @@
         <v>2.7923969999999999E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <v>52</v>
       </c>
@@ -36776,7 +36776,7 @@
         <v>2.3828380000000003E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <v>53</v>
       </c>
@@ -36928,7 +36928,7 @@
         <v>2.4713160000000001E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <v>54</v>
       </c>
@@ -37080,7 +37080,7 @@
         <v>2.369959E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <v>55</v>
       </c>
@@ -37232,7 +37232,7 @@
         <v>2.7680859999999995E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A42" s="6">
         <v>56</v>
       </c>
@@ -37384,7 +37384,7 @@
         <v>2.7324529999999996E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A43" s="6">
         <v>57</v>
       </c>
@@ -37536,7 +37536,7 @@
         <v>2.3671579999999998E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A44" s="6">
         <v>58</v>
       </c>
@@ -37688,7 +37688,7 @@
         <v>2.8590329999999997E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A45" s="6">
         <v>59</v>
       </c>
@@ -37840,7 +37840,7 @@
         <v>2.8783280000000001E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A46" s="6">
         <v>60</v>
       </c>
@@ -37992,7 +37992,7 @@
         <v>3.0878620000000002E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A47" s="6">
         <v>61</v>
       </c>
@@ -38144,7 +38144,7 @@
         <v>3.6834689000000004E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A48" s="6">
         <v>62</v>
       </c>
@@ -38296,7 +38296,7 @@
         <v>4.2790757999999998E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A49" s="6">
         <v>63</v>
       </c>
@@ -38448,7 +38448,7 @@
         <v>4.8746827E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A50" s="6">
         <v>64</v>
       </c>
@@ -38600,7 +38600,7 @@
         <v>5.4702896000000001E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A51" s="6">
         <v>65</v>
       </c>
@@ -38752,7 +38752,7 @@
         <v>6.0658965000000009E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A52" s="6">
         <v>66</v>
       </c>
@@ -38904,7 +38904,7 @@
         <v>6.661503399999999E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A53" s="6">
         <v>67</v>
       </c>
@@ -39056,7 +39056,7 @@
         <v>7.2571102999999998E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A54" s="6">
         <v>68</v>
       </c>
@@ -39208,7 +39208,7 @@
         <v>7.8527172000000006E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A55" s="6">
         <v>69</v>
       </c>
@@ -39360,7 +39360,7 @@
         <v>8.4483241000000001E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A56" s="6">
         <v>70</v>
       </c>
@@ -39512,7 +39512,7 @@
         <v>9.0439310000000009E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A57" s="6">
         <v>71</v>
       </c>
@@ -39664,7 +39664,7 @@
         <v>9.6395379000000017E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A58" s="6">
         <v>72</v>
       </c>
@@ -39816,7 +39816,7 @@
         <v>0.102351448</v>
       </c>
     </row>
-    <row r="59" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A59" s="6">
         <v>73</v>
       </c>
@@ -39968,7 +39968,7 @@
         <v>0.10830751699999999</v>
       </c>
     </row>
-    <row r="60" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A60" s="6">
         <v>74</v>
       </c>
@@ -40120,7 +40120,7 @@
         <v>0.114263586</v>
       </c>
     </row>
-    <row r="61" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A61" s="6">
         <v>75</v>
       </c>
@@ -40272,7 +40272,7 @@
         <v>0.12021965500000002</v>
       </c>
     </row>
-    <row r="62" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A62" s="6">
         <v>76</v>
       </c>
@@ -40424,7 +40424,7 @@
         <v>0.12617572400000002</v>
       </c>
     </row>
-    <row r="63" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A63" s="6">
         <v>77</v>
       </c>
@@ -40576,7 +40576,7 @@
         <v>0.13213179300000003</v>
       </c>
     </row>
-    <row r="64" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A64" s="6">
         <v>78</v>
       </c>
@@ -40728,7 +40728,7 @@
         <v>0.13808786200000003</v>
       </c>
     </row>
-    <row r="65" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A65" s="6">
         <v>79</v>
       </c>
@@ -40880,7 +40880,7 @@
         <v>0.14404393100000004</v>
       </c>
     </row>
-    <row r="66" spans="1:50" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A66" s="6">
         <v>80</v>
       </c>
@@ -41040,9 +41040,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B31A884-F39B-4D2D-93E0-D88DBF495E2F}">
   <dimension ref="A1:T19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>61</v>
       </c>
@@ -41104,7 +41104,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>44</v>
       </c>
@@ -41166,7 +41166,7 @@
         <v>-3.5416304283025245E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
         <v>45</v>
       </c>
@@ -41228,7 +41228,7 @@
         <v>-0.14885284238427224</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="16" t="s">
         <v>46</v>
       </c>
@@ -41290,7 +41290,7 @@
         <v>-0.14903612693976501</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="16" t="s">
         <v>47</v>
       </c>
@@ -41352,7 +41352,7 @@
         <v>-0.1488505184012999</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="16" t="s">
         <v>48</v>
       </c>
@@ -41414,7 +41414,7 @@
         <v>-0.14876549571684003</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" s="16" t="s">
         <v>49</v>
       </c>
@@ -41476,7 +41476,7 @@
         <v>-2.7898746371138178E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
         <v>50</v>
       </c>
@@ -41538,7 +41538,7 @@
         <v>-1.3372169426667689E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="17" t="s">
         <v>51</v>
       </c>
@@ -41600,7 +41600,7 @@
         <v>-1.0928944726124046E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" s="17" t="s">
         <v>52</v>
       </c>
@@ -41662,7 +41662,7 @@
         <v>-1.083806253243007E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" s="17" t="s">
         <v>53</v>
       </c>
@@ -41724,7 +41724,7 @@
         <v>-1.0932388016875905E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" s="17" t="s">
         <v>54</v>
       </c>
@@ -41786,7 +41786,7 @@
         <v>-1.0672934281322143E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" s="17" t="s">
         <v>55</v>
       </c>
@@ -41848,7 +41848,7 @@
         <v>-1.1843326275247906E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
         <v>56</v>
       </c>
@@ -41910,7 +41910,7 @@
         <v>-1.0244321912134775E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" s="17" t="s">
         <v>57</v>
       </c>
@@ -41972,7 +41972,7 @@
         <v>-1.0319993005708817E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" s="17" t="s">
         <v>58</v>
       </c>
@@ -42034,7 +42034,7 @@
         <v>-1.1885693202050004E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" s="17" t="s">
         <v>59</v>
       </c>
@@ -42096,7 +42096,7 @@
         <v>-1.1455520606228623E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" s="17" t="s">
         <v>60</v>
       </c>
@@ -42158,7 +42158,7 @@
         <v>-1.0293612120358798E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" s="17" t="s">
         <v>39</v>
       </c>
@@ -42228,9 +42228,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8FA253C-38A9-483B-BC7F-FF4D6A7E64FE}">
   <dimension ref="A1:T19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>61</v>
       </c>
@@ -42292,7 +42292,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>44</v>
       </c>
@@ -42354,7 +42354,7 @@
         <v>-3.5443995150077267E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
         <v>45</v>
       </c>
@@ -42416,7 +42416,7 @@
         <v>-8.4109512923886201E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="16" t="s">
         <v>46</v>
       </c>
@@ -42478,7 +42478,7 @@
         <v>-8.4687050220290556E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="16" t="s">
         <v>47</v>
       </c>
@@ -42540,7 +42540,7 @@
         <v>-8.6352108125011956E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="16" t="s">
         <v>48</v>
       </c>
@@ -42602,7 +42602,7 @@
         <v>-8.3725315998750289E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" s="16" t="s">
         <v>49</v>
       </c>
@@ -42664,7 +42664,7 @@
         <v>-1.1878865375397826E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
         <v>50</v>
       </c>
@@ -42726,7 +42726,7 @@
         <v>-4.625211430212983E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="17" t="s">
         <v>51</v>
       </c>
@@ -42788,7 +42788,7 @@
         <v>-4.6079895815085634E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" s="17" t="s">
         <v>52</v>
       </c>
@@ -42850,7 +42850,7 @@
         <v>-4.3138027375580488E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" s="17" t="s">
         <v>53</v>
       </c>
@@ -42912,7 +42912,7 @@
         <v>-4.157398398245484E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" s="17" t="s">
         <v>54</v>
       </c>
@@ -42974,7 +42974,7 @@
         <v>-4.2006316563503454E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" s="17" t="s">
         <v>55</v>
       </c>
@@ -43036,7 +43036,7 @@
         <v>-4.6378269229101184E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
         <v>56</v>
       </c>
@@ -43098,7 +43098,7 @@
         <v>-4.4640337855897348E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" s="17" t="s">
         <v>57</v>
       </c>
@@ -43160,7 +43160,7 @@
         <v>-4.3047756070677696E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" s="17" t="s">
         <v>58</v>
       </c>
@@ -43222,7 +43222,7 @@
         <v>-4.2685847954493936E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" s="17" t="s">
         <v>59</v>
       </c>
@@ -43284,7 +43284,7 @@
         <v>-4.4973015013057404E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" s="17" t="s">
         <v>60</v>
       </c>
@@ -43346,7 +43346,7 @@
         <v>-4.3900487142188183E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" s="17" t="s">
         <v>39</v>
       </c>
@@ -43416,9 +43416,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE83AD0B-62F5-4A81-BCDC-3EC820E3DC16}">
   <dimension ref="A1:T19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>61</v>
       </c>
@@ -43480,7 +43480,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>44</v>
       </c>
@@ -43542,7 +43542,7 @@
         <v>-7.1613088912057851E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
         <v>45</v>
       </c>
@@ -43604,7 +43604,7 @@
         <v>-1.9526381793252119E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="16" t="s">
         <v>46</v>
       </c>
@@ -43666,7 +43666,7 @@
         <v>-1.88822206336366E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="16" t="s">
         <v>47</v>
       </c>
@@ -43728,7 +43728,7 @@
         <v>-1.8927494064318144E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="16" t="s">
         <v>48</v>
       </c>
@@ -43790,7 +43790,7 @@
         <v>-1.9315815848071835E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" s="16" t="s">
         <v>49</v>
       </c>
@@ -43852,7 +43852,7 @@
         <v>-1.6565968080052413E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
         <v>50</v>
       </c>
@@ -43914,7 +43914,7 @@
         <v>-4.1902413783987194E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="17" t="s">
         <v>51</v>
       </c>
@@ -43976,7 +43976,7 @@
         <v>-4.444529060319247E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" s="17" t="s">
         <v>52</v>
       </c>
@@ -44038,7 +44038,7 @@
         <v>-4.6917220426184961E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" s="17" t="s">
         <v>53</v>
       </c>
@@ -44100,7 +44100,7 @@
         <v>-4.3920575431861328E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" s="17" t="s">
         <v>54</v>
       </c>
@@ -44162,7 +44162,7 @@
         <v>-2.5272066550653602E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" s="17" t="s">
         <v>55</v>
       </c>
@@ -44224,7 +44224,7 @@
         <v>-3.7694427074636896E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
         <v>56</v>
       </c>
@@ -44286,7 +44286,7 @@
         <v>-4.0636389562362174E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" s="17" t="s">
         <v>57</v>
       </c>
@@ -44348,7 +44348,7 @@
         <v>-4.6529172380434117E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" s="17" t="s">
         <v>58</v>
       </c>
@@ -44410,7 +44410,7 @@
         <v>-3.9940166814911053E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" s="17" t="s">
         <v>59</v>
       </c>
@@ -44472,7 +44472,7 @@
         <v>-3.3260633146255346E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" s="17" t="s">
         <v>60</v>
       </c>
@@ -44534,7 +44534,7 @@
         <v>-4.3689659654760479E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" s="17" t="s">
         <v>39</v>
       </c>
@@ -44604,9 +44604,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{298225BB-FD6B-487D-8E0A-5B17245B7D37}">
   <dimension ref="A1:T19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>61</v>
       </c>
@@ -44668,7 +44668,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>44</v>
       </c>
@@ -44730,7 +44730,7 @@
         <v>-8.0884031096164523E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
         <v>45</v>
       </c>
@@ -44792,7 +44792,7 @@
         <v>-4.7159132329863641E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="16" t="s">
         <v>46</v>
       </c>
@@ -44854,7 +44854,7 @@
         <v>-4.8747912666294397E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="16" t="s">
         <v>47</v>
       </c>
@@ -44916,7 +44916,7 @@
         <v>-4.6445781622898585E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="16" t="s">
         <v>48</v>
       </c>
@@ -44978,7 +44978,7 @@
         <v>-4.9030571989960624E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" s="16" t="s">
         <v>49</v>
       </c>
@@ -45040,7 +45040,7 @@
         <v>-6.736439180099811E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
         <v>50</v>
       </c>
@@ -45102,7 +45102,7 @@
         <v>-2.7998613131418881E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="17" t="s">
         <v>51</v>
       </c>
@@ -45164,7 +45164,7 @@
         <v>-2.7045184444692435E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" s="17" t="s">
         <v>52</v>
       </c>
@@ -45226,7 +45226,7 @@
         <v>-2.7228858565888892E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" s="17" t="s">
         <v>53</v>
       </c>
@@ -45288,7 +45288,7 @@
         <v>-2.6261043632189495E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" s="17" t="s">
         <v>54</v>
       </c>
@@ -45350,7 +45350,7 @@
         <v>-2.5854586257496267E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" s="17" t="s">
         <v>55</v>
       </c>
@@ -45412,7 +45412,7 @@
         <v>-2.5922132986329867E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
         <v>56</v>
       </c>
@@ -45474,7 +45474,7 @@
         <v>-2.7112357921276072E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" s="17" t="s">
         <v>57</v>
       </c>
@@ -45536,7 +45536,7 @@
         <v>-2.4417308246975724E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" s="17" t="s">
         <v>58</v>
       </c>
@@ -45598,7 +45598,7 @@
         <v>-2.6761462165507013E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" s="17" t="s">
         <v>59</v>
       </c>
@@ -45660,7 +45660,7 @@
         <v>-2.6494193995736386E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" s="17" t="s">
         <v>60</v>
       </c>
@@ -45722,7 +45722,7 @@
         <v>-2.6607686203638042E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" s="17" t="s">
         <v>39</v>
       </c>
@@ -45792,17 +45792,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D29755F-03F5-4832-BD4A-46B3397AFE2F}">
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.7265625" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="7"/>
       <c r="B2" s="8" t="s">
         <v>32</v>
@@ -45814,7 +45814,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -45828,7 +45828,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -45836,7 +45836,7 @@
       <c r="C4" s="11"/>
       <c r="D4" s="9"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -45850,7 +45850,7 @@
         <v>0.47399999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -45864,7 +45864,7 @@
         <v>0.60599999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -45878,7 +45878,7 @@
         <v>0.26900000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -45892,7 +45892,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -45906,7 +45906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -45914,7 +45914,7 @@
       <c r="C10" s="11"/>
       <c r="D10" s="9"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -45928,7 +45928,7 @@
         <v>0.67600000000000005</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -45942,7 +45942,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -45956,7 +45956,7 @@
         <v>0.65300000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -45970,7 +45970,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -45984,7 +45984,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -45998,7 +45998,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -46012,7 +46012,7 @@
         <v>0.95799999999999996</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -46026,7 +46026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -46040,7 +46040,7 @@
         <v>0.80100000000000005</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -46054,7 +46054,7 @@
         <v>0.19500000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -46068,7 +46068,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>39</v>
       </c>
@@ -46082,7 +46082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -46090,7 +46090,7 @@
         <v>42528</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>41</v>
       </c>
@@ -46098,7 +46098,7 @@
         <v>3.6499999999999998E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>42</v>
       </c>
@@ -46108,7 +46108,7 @@
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
     </row>
-    <row r="26" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="1:4" ht="16" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -46117,18 +46117,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A03763CC-A86A-48D7-B741-040395EE32CB}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.7265625" customWidth="1"/>
-    <col min="2" max="2" width="10.453125" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="7"/>
       <c r="B2" s="8" t="s">
         <v>32</v>
@@ -46140,7 +46140,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -46156,7 +46156,7 @@
       <c r="F3" s="15"/>
       <c r="G3" s="15"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -46166,7 +46166,7 @@
       <c r="F4" s="15"/>
       <c r="G4" s="15"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -46182,7 +46182,7 @@
       <c r="F5" s="15"/>
       <c r="G5" s="15"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -46198,7 +46198,7 @@
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -46214,7 +46214,7 @@
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -46230,7 +46230,7 @@
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -46246,7 +46246,7 @@
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -46256,7 +46256,7 @@
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -46272,7 +46272,7 @@
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -46288,7 +46288,7 @@
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -46304,7 +46304,7 @@
       <c r="F13" s="15"/>
       <c r="G13" s="15"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -46320,7 +46320,7 @@
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -46336,7 +46336,7 @@
       <c r="F15" s="15"/>
       <c r="G15" s="15"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -46352,7 +46352,7 @@
       <c r="F16" s="15"/>
       <c r="G16" s="15"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -46367,7 +46367,7 @@
       </c>
       <c r="F17" s="15"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -46382,7 +46382,7 @@
       </c>
       <c r="F18" s="15"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -46397,7 +46397,7 @@
       </c>
       <c r="F19" s="15"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -46412,7 +46412,7 @@
       </c>
       <c r="F20" s="15"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -46426,7 +46426,7 @@
         <v>0.496</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>39</v>
       </c>
@@ -46440,7 +46440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -46448,7 +46448,7 @@
         <v>105239</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>41</v>
       </c>
@@ -46456,7 +46456,7 @@
         <v>8.14E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>42</v>
       </c>
@@ -46466,7 +46466,7 @@
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
     </row>
-    <row r="26" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="1:6" ht="16" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -46475,18 +46475,18 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1700754-15D1-4FAA-B4AF-AB487BD81AF9}">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.7265625" customWidth="1"/>
-    <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="7"/>
       <c r="B2" s="8" t="s">
         <v>32</v>
@@ -46498,7 +46498,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -46514,7 +46514,7 @@
       <c r="F3" s="15"/>
       <c r="H3" s="15"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -46524,7 +46524,7 @@
       <c r="F4" s="15"/>
       <c r="H4" s="15"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -46540,7 +46540,7 @@
       <c r="F5" s="15"/>
       <c r="H5" s="15"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -46556,7 +46556,7 @@
       <c r="F6" s="15"/>
       <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -46572,7 +46572,7 @@
       <c r="F7" s="15"/>
       <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -46588,7 +46588,7 @@
       <c r="F8" s="15"/>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -46604,7 +46604,7 @@
       <c r="F9" s="15"/>
       <c r="H9" s="15"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -46614,7 +46614,7 @@
       <c r="F10" s="15"/>
       <c r="H10" s="15"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -46630,7 +46630,7 @@
       <c r="F11" s="15"/>
       <c r="H11" s="15"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -46646,7 +46646,7 @@
       <c r="F12" s="15"/>
       <c r="H12" s="15"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -46662,7 +46662,7 @@
       <c r="F13" s="15"/>
       <c r="H13" s="15"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -46678,7 +46678,7 @@
       <c r="F14" s="15"/>
       <c r="H14" s="15"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -46694,7 +46694,7 @@
       <c r="F15" s="15"/>
       <c r="H15" s="15"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -46710,7 +46710,7 @@
       <c r="F16" s="15"/>
       <c r="H16" s="15"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -46726,7 +46726,7 @@
       <c r="F17" s="15"/>
       <c r="H17" s="15"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -46742,7 +46742,7 @@
       <c r="F18" s="15"/>
       <c r="H18" s="15"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -46758,7 +46758,7 @@
       <c r="F19" s="15"/>
       <c r="H19" s="15"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -46774,7 +46774,7 @@
       <c r="F20" s="15"/>
       <c r="H20" s="15"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -46788,7 +46788,7 @@
         <v>0.90100000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>39</v>
       </c>
@@ -46802,7 +46802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -46810,7 +46810,7 @@
         <v>51984</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>41</v>
       </c>
@@ -46818,7 +46818,7 @@
         <v>2.7699999999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>42</v>
       </c>
@@ -46828,7 +46828,7 @@
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
     </row>
-    <row r="26" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="1:8" ht="16" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -46837,18 +46837,18 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC354731-ABAD-4A25-A806-32C67693DC3F}">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.7265625" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="7"/>
       <c r="B2" s="8" t="s">
         <v>32</v>
@@ -46860,7 +46860,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -46876,7 +46876,7 @@
       <c r="G3" s="15"/>
       <c r="H3" s="15"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -46886,7 +46886,7 @@
       <c r="G4" s="15"/>
       <c r="H4" s="15"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -46902,7 +46902,7 @@
       <c r="G5" s="15"/>
       <c r="H5" s="15"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -46918,7 +46918,7 @@
       <c r="G6" s="15"/>
       <c r="H6" s="15"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -46934,7 +46934,7 @@
       <c r="G7" s="15"/>
       <c r="H7" s="15"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -46950,7 +46950,7 @@
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -46966,7 +46966,7 @@
       <c r="G9" s="15"/>
       <c r="H9" s="15"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -46976,7 +46976,7 @@
       <c r="G10" s="15"/>
       <c r="H10" s="15"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -46992,7 +46992,7 @@
       <c r="G11" s="15"/>
       <c r="H11" s="15"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -47008,7 +47008,7 @@
       <c r="G12" s="15"/>
       <c r="H12" s="15"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -47024,7 +47024,7 @@
       <c r="G13" s="15"/>
       <c r="H13" s="15"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -47040,7 +47040,7 @@
       <c r="G14" s="15"/>
       <c r="H14" s="15"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -47056,7 +47056,7 @@
       <c r="G15" s="15"/>
       <c r="H15" s="15"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -47072,7 +47072,7 @@
       <c r="G16" s="15"/>
       <c r="H16" s="15"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -47088,7 +47088,7 @@
       <c r="G17" s="15"/>
       <c r="H17" s="15"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -47104,7 +47104,7 @@
       <c r="G18" s="15"/>
       <c r="H18" s="15"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -47120,7 +47120,7 @@
       <c r="G19" s="15"/>
       <c r="H19" s="15"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -47136,7 +47136,7 @@
       <c r="G20" s="15"/>
       <c r="H20" s="15"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -47150,7 +47150,7 @@
         <v>0.98799999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>39</v>
       </c>
@@ -47164,7 +47164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -47172,7 +47172,7 @@
         <v>124166</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>41</v>
       </c>
@@ -47180,7 +47180,7 @@
         <v>5.8099999999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>42</v>
       </c>
@@ -47190,7 +47190,7 @@
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
     </row>
-    <row r="26" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="1:8" ht="16" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
